--- a/DATA/canonical/REGIONAL_GVA.xlsx
+++ b/DATA/canonical/REGIONAL_GVA.xlsx
@@ -961,7 +961,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1555"/>
+  <dimension ref="A1:F1666"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -32063,9 +32063,2229 @@
         <v>A</v>
       </c>
     </row>
+    <row r="1556">
+      <c r="A1556" t="str">
+        <v>_T</v>
+      </c>
+      <c r="B1556" t="str">
+        <v>_T</v>
+      </c>
+      <c r="C1556" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1556" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1556">
+        <v>93022.2753157054</v>
+      </c>
+      <c r="F1556" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="str">
+        <v>R10</v>
+      </c>
+      <c r="B1557" t="str">
+        <v>_T</v>
+      </c>
+      <c r="C1557" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1557" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1557">
+        <v>2855.43699965871</v>
+      </c>
+      <c r="F1557" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="str">
+        <v>R10</v>
+      </c>
+      <c r="B1558" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1558" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1558" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1558">
+        <v>439.923570041185</v>
+      </c>
+      <c r="F1558" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="str">
+        <v>R10</v>
+      </c>
+      <c r="B1559" t="str">
+        <v>12</v>
+      </c>
+      <c r="C1559" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1559" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1559">
+        <v>210.1430140339404</v>
+      </c>
+      <c r="F1559" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="str">
+        <v>R10</v>
+      </c>
+      <c r="B1560" t="str">
+        <v>15</v>
+      </c>
+      <c r="C1560" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1560" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1560">
+        <v>253.24883880785222</v>
+      </c>
+      <c r="F1560" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="str">
+        <v>R10</v>
+      </c>
+      <c r="B1561" t="str">
+        <v>16</v>
+      </c>
+      <c r="C1561" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1561" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1561">
+        <v>233.10574565018598</v>
+      </c>
+      <c r="F1561" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="str">
+        <v>R10</v>
+      </c>
+      <c r="B1562" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1562" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1562" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1562">
+        <v>555.308800464235</v>
+      </c>
+      <c r="F1562" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="str">
+        <v>R10</v>
+      </c>
+      <c r="B1563" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1563" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1563" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1563">
+        <v>133.304128770617</v>
+      </c>
+      <c r="F1563" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="str">
+        <v>R10</v>
+      </c>
+      <c r="B1564" t="str">
+        <v>7</v>
+      </c>
+      <c r="C1564" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1564" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1564">
+        <v>74.058426491317</v>
+      </c>
+      <c r="F1564" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="str">
+        <v>R10</v>
+      </c>
+      <c r="B1565" t="str">
+        <v>8</v>
+      </c>
+      <c r="C1565" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1565" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1565">
+        <v>48.00384677491626</v>
+      </c>
+      <c r="F1565" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="str">
+        <v>R10</v>
+      </c>
+      <c r="B1566" t="str">
+        <v>OTH</v>
+      </c>
+      <c r="C1566" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1566" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1566">
+        <v>538.6700351280542</v>
+      </c>
+      <c r="F1566" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="str">
+        <v>R11</v>
+      </c>
+      <c r="B1567" t="str">
+        <v>_T</v>
+      </c>
+      <c r="C1567" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1567" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1567">
+        <v>6638.03769475541</v>
+      </c>
+      <c r="F1567" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="str">
+        <v>R11</v>
+      </c>
+      <c r="B1568" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1568" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1568" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1568">
+        <v>815.4409486280607</v>
+      </c>
+      <c r="F1568" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="str">
+        <v>R11</v>
+      </c>
+      <c r="B1569" t="str">
+        <v>12</v>
+      </c>
+      <c r="C1569" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1569" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1569">
+        <v>286.74234397278104</v>
+      </c>
+      <c r="F1569" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="str">
+        <v>R11</v>
+      </c>
+      <c r="B1570" t="str">
+        <v>15</v>
+      </c>
+      <c r="C1570" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1570" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1570">
+        <v>552.8492076672101</v>
+      </c>
+      <c r="F1570" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="str">
+        <v>R11</v>
+      </c>
+      <c r="B1571" t="str">
+        <v>16</v>
+      </c>
+      <c r="C1571" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1571" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1571">
+        <v>330.66729965538474</v>
+      </c>
+      <c r="F1571" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="str">
+        <v>R11</v>
+      </c>
+      <c r="B1572" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1572" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1572" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1572">
+        <v>928.867731434104</v>
+      </c>
+      <c r="F1572" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="str">
+        <v>R11</v>
+      </c>
+      <c r="B1573" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1573" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1573" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1573">
+        <v>201.15565191874668</v>
+      </c>
+      <c r="F1573" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="str">
+        <v>R11</v>
+      </c>
+      <c r="B1574" t="str">
+        <v>7</v>
+      </c>
+      <c r="C1574" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1574" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1574">
+        <v>335.4227871154726</v>
+      </c>
+      <c r="F1574" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="str">
+        <v>R11</v>
+      </c>
+      <c r="B1575" t="str">
+        <v>8</v>
+      </c>
+      <c r="C1575" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1575" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1575">
+        <v>121.399971360031</v>
+      </c>
+      <c r="F1575" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="str">
+        <v>R11</v>
+      </c>
+      <c r="B1576" t="str">
+        <v>OTH</v>
+      </c>
+      <c r="C1576" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1576" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1576">
+        <v>2206.118096864454</v>
+      </c>
+      <c r="F1576" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="str">
+        <v>R12</v>
+      </c>
+      <c r="B1577" t="str">
+        <v>_T</v>
+      </c>
+      <c r="C1577" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1577" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1577">
+        <v>3922.758188874017</v>
+      </c>
+      <c r="F1577" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="str">
+        <v>R12</v>
+      </c>
+      <c r="B1578" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1578" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1578" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1578">
+        <v>575.805767214249</v>
+      </c>
+      <c r="F1578" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="str">
+        <v>R12</v>
+      </c>
+      <c r="B1579" t="str">
+        <v>12</v>
+      </c>
+      <c r="C1579" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1579" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1579">
+        <v>170.34373197547058</v>
+      </c>
+      <c r="F1579" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="str">
+        <v>R12</v>
+      </c>
+      <c r="B1580" t="str">
+        <v>15</v>
+      </c>
+      <c r="C1580" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1580" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1580">
+        <v>546.697175046743</v>
+      </c>
+      <c r="F1580" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="str">
+        <v>R12</v>
+      </c>
+      <c r="B1581" t="str">
+        <v>16</v>
+      </c>
+      <c r="C1581" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1581" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1581">
+        <v>281.21757794322855</v>
+      </c>
+      <c r="F1581" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="str">
+        <v>R12</v>
+      </c>
+      <c r="B1582" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1582" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1582" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1582">
+        <v>545.674817683674</v>
+      </c>
+      <c r="F1582" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="str">
+        <v>R12</v>
+      </c>
+      <c r="B1583" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1583" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1583" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1583">
+        <v>146.59757161902223</v>
+      </c>
+      <c r="F1583" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="str">
+        <v>R12</v>
+      </c>
+      <c r="B1584" t="str">
+        <v>7</v>
+      </c>
+      <c r="C1584" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1584" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1584">
+        <v>194.5094792594277</v>
+      </c>
+      <c r="F1584" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="str">
+        <v>R12</v>
+      </c>
+      <c r="B1585" t="str">
+        <v>8</v>
+      </c>
+      <c r="C1585" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1585" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1585">
+        <v>116.45365214241374</v>
+      </c>
+      <c r="F1585" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="str">
+        <v>R12</v>
+      </c>
+      <c r="B1586" t="str">
+        <v>OTH</v>
+      </c>
+      <c r="C1586" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1586" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1586">
+        <v>837.610283463217</v>
+      </c>
+      <c r="F1586" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="str">
+        <v>R2</v>
+      </c>
+      <c r="B1587" t="str">
+        <v>_T</v>
+      </c>
+      <c r="C1587" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1587" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1587">
+        <v>49374.72070890671</v>
+      </c>
+      <c r="F1587" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="str">
+        <v>R2</v>
+      </c>
+      <c r="B1588" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1588" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1588" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1588">
+        <v>62.03553917771869</v>
+      </c>
+      <c r="F1588" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="str">
+        <v>R2</v>
+      </c>
+      <c r="B1589" t="str">
+        <v>12</v>
+      </c>
+      <c r="C1589" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1589" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1589">
+        <v>4700.289737980919</v>
+      </c>
+      <c r="F1589" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="str">
+        <v>R2</v>
+      </c>
+      <c r="B1590" t="str">
+        <v>15</v>
+      </c>
+      <c r="C1590" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1590" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1590">
+        <v>1934.1174785529</v>
+      </c>
+      <c r="F1590" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="str">
+        <v>R2</v>
+      </c>
+      <c r="B1591" t="str">
+        <v>16</v>
+      </c>
+      <c r="C1591" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1591" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1591">
+        <v>1561.5143351639804</v>
+      </c>
+      <c r="F1591" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="str">
+        <v>R2</v>
+      </c>
+      <c r="B1592" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1592" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1592" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1592">
+        <v>2789.18433881029</v>
+      </c>
+      <c r="F1592" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="str">
+        <v>R2</v>
+      </c>
+      <c r="B1593" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1593" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1593" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1593">
+        <v>4455.10860689624</v>
+      </c>
+      <c r="F1593" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="str">
+        <v>R2</v>
+      </c>
+      <c r="B1594" t="str">
+        <v>7</v>
+      </c>
+      <c r="C1594" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1594" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1594">
+        <v>10207.1705496639</v>
+      </c>
+      <c r="F1594" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="str">
+        <v>R2</v>
+      </c>
+      <c r="B1595" t="str">
+        <v>8</v>
+      </c>
+      <c r="C1595" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1595" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1595">
+        <v>3110.1584671160263</v>
+      </c>
+      <c r="F1595" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="str">
+        <v>R2</v>
+      </c>
+      <c r="B1596" t="str">
+        <v>OTH</v>
+      </c>
+      <c r="C1596" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1596" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1596">
+        <v>14162.991413615924</v>
+      </c>
+      <c r="F1596" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="str">
+        <v>R3</v>
+      </c>
+      <c r="B1597" t="str">
+        <v>_T</v>
+      </c>
+      <c r="C1597" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1597" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1597">
+        <v>8634.02452689686</v>
+      </c>
+      <c r="F1597" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="str">
+        <v>R3</v>
+      </c>
+      <c r="B1598" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1598" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1598" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1598">
+        <v>190.00140324118337</v>
+      </c>
+      <c r="F1598" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="str">
+        <v>R3</v>
+      </c>
+      <c r="B1599" t="str">
+        <v>12</v>
+      </c>
+      <c r="C1599" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1599" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1599">
+        <v>944.6120739155264</v>
+      </c>
+      <c r="F1599" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="str">
+        <v>R3</v>
+      </c>
+      <c r="B1600" t="str">
+        <v>15</v>
+      </c>
+      <c r="C1600" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1600" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1600">
+        <v>460.3657522852588</v>
+      </c>
+      <c r="F1600" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="str">
+        <v>R3</v>
+      </c>
+      <c r="B1601" t="str">
+        <v>16</v>
+      </c>
+      <c r="C1601" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1601" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1601">
+        <v>441.1323974904982</v>
+      </c>
+      <c r="F1601" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="str">
+        <v>R3</v>
+      </c>
+      <c r="B1602" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1602" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1602" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1602">
+        <v>431.8941290728036</v>
+      </c>
+      <c r="F1602" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="str">
+        <v>R3</v>
+      </c>
+      <c r="B1603" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1603" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1603" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1603">
+        <v>1107.6193144960998</v>
+      </c>
+      <c r="F1603" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="str">
+        <v>R3</v>
+      </c>
+      <c r="B1604" t="str">
+        <v>7</v>
+      </c>
+      <c r="C1604" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1604" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1604">
+        <v>714.6756033702383</v>
+      </c>
+      <c r="F1604" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="str">
+        <v>R3</v>
+      </c>
+      <c r="B1605" t="str">
+        <v>8</v>
+      </c>
+      <c r="C1605" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1605" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1605">
+        <v>609.5951642290366</v>
+      </c>
+      <c r="F1605" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="str">
+        <v>R3</v>
+      </c>
+      <c r="B1606" t="str">
+        <v>OTH</v>
+      </c>
+      <c r="C1606" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1606" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1606">
+        <v>2616.350579350274</v>
+      </c>
+      <c r="F1606" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="str">
+        <v>R4</v>
+      </c>
+      <c r="B1607" t="str">
+        <v>_T</v>
+      </c>
+      <c r="C1607" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1607" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1607">
+        <v>1559.2571093341091</v>
+      </c>
+      <c r="F1607" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="str">
+        <v>R4</v>
+      </c>
+      <c r="B1608" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1608" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1608" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1608">
+        <v>207.66270153280558</v>
+      </c>
+      <c r="F1608" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="str">
+        <v>R4</v>
+      </c>
+      <c r="B1609" t="str">
+        <v>12</v>
+      </c>
+      <c r="C1609" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1609" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1609">
+        <v>189.58996903198593</v>
+      </c>
+      <c r="F1609" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="str">
+        <v>R4</v>
+      </c>
+      <c r="B1610" t="str">
+        <v>15</v>
+      </c>
+      <c r="C1610" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1610" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1610">
+        <v>145.3719179002068</v>
+      </c>
+      <c r="F1610" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="str">
+        <v>R4</v>
+      </c>
+      <c r="B1611" t="str">
+        <v>16</v>
+      </c>
+      <c r="C1611" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1611" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1611">
+        <v>166.76884943258028</v>
+      </c>
+      <c r="F1611" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="str">
+        <v>R4</v>
+      </c>
+      <c r="B1612" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1612" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1612" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1612">
+        <v>133.94225425157902</v>
+      </c>
+      <c r="F1612" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="str">
+        <v>R4</v>
+      </c>
+      <c r="B1613" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1613" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1613" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1613">
+        <v>31.9395983267701</v>
+      </c>
+      <c r="F1613" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="str">
+        <v>R4</v>
+      </c>
+      <c r="B1614" t="str">
+        <v>7</v>
+      </c>
+      <c r="C1614" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1614" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1614">
+        <v>51.50100711097399</v>
+      </c>
+      <c r="F1614" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="str">
+        <v>R4</v>
+      </c>
+      <c r="B1615" t="str">
+        <v>8</v>
+      </c>
+      <c r="C1615" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1615" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1615">
+        <v>30.816534567521302</v>
+      </c>
+      <c r="F1615" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="str">
+        <v>R4</v>
+      </c>
+      <c r="B1616" t="str">
+        <v>OTH</v>
+      </c>
+      <c r="C1616" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1616" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1616">
+        <v>399.7997285694637</v>
+      </c>
+      <c r="F1616" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="str">
+        <v>R5</v>
+      </c>
+      <c r="B1617" t="str">
+        <v>_T</v>
+      </c>
+      <c r="C1617" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1617" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1617">
+        <v>7203.151022643833</v>
+      </c>
+      <c r="F1617" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="str">
+        <v>R5</v>
+      </c>
+      <c r="B1618" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1618" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1618" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1618">
+        <v>715.676721667705</v>
+      </c>
+      <c r="F1618" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="str">
+        <v>R5</v>
+      </c>
+      <c r="B1619" t="str">
+        <v>12</v>
+      </c>
+      <c r="C1619" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1619" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1619">
+        <v>606.7298908649109</v>
+      </c>
+      <c r="F1619" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="str">
+        <v>R5</v>
+      </c>
+      <c r="B1620" t="str">
+        <v>15</v>
+      </c>
+      <c r="C1620" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1620" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1620">
+        <v>578.982878974096</v>
+      </c>
+      <c r="F1620" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="str">
+        <v>R5</v>
+      </c>
+      <c r="B1621" t="str">
+        <v>16</v>
+      </c>
+      <c r="C1621" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1621" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1621">
+        <v>613.94913887969</v>
+      </c>
+      <c r="F1621" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="str">
+        <v>R5</v>
+      </c>
+      <c r="B1622" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1622" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1622" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1622">
+        <v>633.030107126347</v>
+      </c>
+      <c r="F1622" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="str">
+        <v>R5</v>
+      </c>
+      <c r="B1623" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1623" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1623" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1623">
+        <v>439.4928344622123</v>
+      </c>
+      <c r="F1623" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="str">
+        <v>R5</v>
+      </c>
+      <c r="B1624" t="str">
+        <v>7</v>
+      </c>
+      <c r="C1624" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1624" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1624">
+        <v>426.9109242516355</v>
+      </c>
+      <c r="F1624" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="str">
+        <v>R5</v>
+      </c>
+      <c r="B1625" t="str">
+        <v>8</v>
+      </c>
+      <c r="C1625" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1625" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1625">
+        <v>157.41028707234764</v>
+      </c>
+      <c r="F1625" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="str">
+        <v>R5</v>
+      </c>
+      <c r="B1626" t="str">
+        <v>OTH</v>
+      </c>
+      <c r="C1626" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1626" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1626">
+        <v>2098.433879839405</v>
+      </c>
+      <c r="F1626" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="str">
+        <v>R6</v>
+      </c>
+      <c r="B1627" t="str">
+        <v>_T</v>
+      </c>
+      <c r="C1627" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1627" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1627">
+        <v>4639.042812994795</v>
+      </c>
+      <c r="F1627" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="str">
+        <v>R6</v>
+      </c>
+      <c r="B1628" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1628" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1628" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1628">
+        <v>1336.5937571893282</v>
+      </c>
+      <c r="F1628" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="str">
+        <v>R6</v>
+      </c>
+      <c r="B1629" t="str">
+        <v>12</v>
+      </c>
+      <c r="C1629" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1629" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1629">
+        <v>246.49079986200024</v>
+      </c>
+      <c r="F1629" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="str">
+        <v>R6</v>
+      </c>
+      <c r="B1630" t="str">
+        <v>15</v>
+      </c>
+      <c r="C1630" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1630" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1630">
+        <v>339.87195621642996</v>
+      </c>
+      <c r="F1630" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="str">
+        <v>R6</v>
+      </c>
+      <c r="B1631" t="str">
+        <v>16</v>
+      </c>
+      <c r="C1631" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1631" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1631">
+        <v>342.4437451899426</v>
+      </c>
+      <c r="F1631" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="str">
+        <v>R6</v>
+      </c>
+      <c r="B1632" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1632" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1632" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1632">
+        <v>477.843938329985</v>
+      </c>
+      <c r="F1632" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="str">
+        <v>R6</v>
+      </c>
+      <c r="B1633" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1633" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1633" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1633">
+        <v>129.4713425579611</v>
+      </c>
+      <c r="F1633" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="str">
+        <v>R6</v>
+      </c>
+      <c r="B1634" t="str">
+        <v>7</v>
+      </c>
+      <c r="C1634" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1634" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1634">
+        <v>150.02419248732153</v>
+      </c>
+      <c r="F1634" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="str">
+        <v>R6</v>
+      </c>
+      <c r="B1635" t="str">
+        <v>8</v>
+      </c>
+      <c r="C1635" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1635" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1635">
+        <v>38.78575407773205</v>
+      </c>
+      <c r="F1635" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="str">
+        <v>R6</v>
+      </c>
+      <c r="B1636" t="str">
+        <v>OTH</v>
+      </c>
+      <c r="C1636" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1636" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1636">
+        <v>976.937552380607</v>
+      </c>
+      <c r="F1636" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="str">
+        <v>R7</v>
+      </c>
+      <c r="B1637" t="str">
+        <v>_T</v>
+      </c>
+      <c r="C1637" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1637" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1637">
+        <v>2545.782678430349</v>
+      </c>
+      <c r="F1637" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="str">
+        <v>R7</v>
+      </c>
+      <c r="B1638" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1638" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1638" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1638">
+        <v>119.46225767217865</v>
+      </c>
+      <c r="F1638" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="str">
+        <v>R7</v>
+      </c>
+      <c r="B1639" t="str">
+        <v>12</v>
+      </c>
+      <c r="C1639" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1639" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1639">
+        <v>253.47471039030086</v>
+      </c>
+      <c r="F1639" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="str">
+        <v>R7</v>
+      </c>
+      <c r="B1640" t="str">
+        <v>15</v>
+      </c>
+      <c r="C1640" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1640" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1640">
+        <v>161.961807201475</v>
+      </c>
+      <c r="F1640" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="str">
+        <v>R7</v>
+      </c>
+      <c r="B1641" t="str">
+        <v>16</v>
+      </c>
+      <c r="C1641" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1641" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1641">
+        <v>123.54363149699724</v>
+      </c>
+      <c r="F1641" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="str">
+        <v>R7</v>
+      </c>
+      <c r="B1642" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1642" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1642" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1642">
+        <v>805.834285040622</v>
+      </c>
+      <c r="F1642" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="str">
+        <v>R7</v>
+      </c>
+      <c r="B1643" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1643" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1643" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1643">
+        <v>60.25601886571251</v>
+      </c>
+      <c r="F1643" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="str">
+        <v>R7</v>
+      </c>
+      <c r="B1644" t="str">
+        <v>7</v>
+      </c>
+      <c r="C1644" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1644" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1644">
+        <v>106.5948929698138</v>
+      </c>
+      <c r="F1644" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="str">
+        <v>R7</v>
+      </c>
+      <c r="B1645" t="str">
+        <v>8</v>
+      </c>
+      <c r="C1645" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1645" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1645">
+        <v>45.32389439870132</v>
+      </c>
+      <c r="F1645" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="str">
+        <v>R7</v>
+      </c>
+      <c r="B1646" t="str">
+        <v>OTH</v>
+      </c>
+      <c r="C1646" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1646" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1646">
+        <v>539.7490555706753</v>
+      </c>
+      <c r="F1646" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="str">
+        <v>R8</v>
+      </c>
+      <c r="B1647" t="str">
+        <v>_T</v>
+      </c>
+      <c r="C1647" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1647" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1647">
+        <v>547.6791591451993</v>
+      </c>
+      <c r="F1647" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="str">
+        <v>R8</v>
+      </c>
+      <c r="B1648" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1648" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1648" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1648">
+        <v>57.70294439604741</v>
+      </c>
+      <c r="F1648" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="str">
+        <v>R8</v>
+      </c>
+      <c r="B1649" t="str">
+        <v>12</v>
+      </c>
+      <c r="C1649" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1649" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1649">
+        <v>34.38313809865898</v>
+      </c>
+      <c r="F1649" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="str">
+        <v>R8</v>
+      </c>
+      <c r="B1650" t="str">
+        <v>15</v>
+      </c>
+      <c r="C1650" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1650" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1650">
+        <v>83.0443534910295</v>
+      </c>
+      <c r="F1650" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="str">
+        <v>R8</v>
+      </c>
+      <c r="B1651" t="str">
+        <v>16</v>
+      </c>
+      <c r="C1651" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1651" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1651">
+        <v>72.20821766090002</v>
+      </c>
+      <c r="F1651" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="str">
+        <v>R8</v>
+      </c>
+      <c r="B1652" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1652" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1652" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1652">
+        <v>33.97473855594859</v>
+      </c>
+      <c r="F1652" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="str">
+        <v>R8</v>
+      </c>
+      <c r="B1653" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1653" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1653" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1653">
+        <v>30.819930208174146</v>
+      </c>
+      <c r="F1653" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="str">
+        <v>R8</v>
+      </c>
+      <c r="B1654" t="str">
+        <v>7</v>
+      </c>
+      <c r="C1654" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1654" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1654">
+        <v>6.514712111899757</v>
+      </c>
+      <c r="F1654" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="str">
+        <v>R8</v>
+      </c>
+      <c r="B1655" t="str">
+        <v>8</v>
+      </c>
+      <c r="C1655" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1655" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1655">
+        <v>2.764268168443451</v>
+      </c>
+      <c r="F1655" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="str">
+        <v>R8</v>
+      </c>
+      <c r="B1656" t="str">
+        <v>OTH</v>
+      </c>
+      <c r="C1656" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1656" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1656">
+        <v>155.36321549440623</v>
+      </c>
+      <c r="F1656" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="str">
+        <v>R9</v>
+      </c>
+      <c r="B1657" t="str">
+        <v>_T</v>
+      </c>
+      <c r="C1657" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1657" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1657">
+        <v>5102.384414065394</v>
+      </c>
+      <c r="F1657" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="str">
+        <v>R9</v>
+      </c>
+      <c r="B1658" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1658" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1658" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1658">
+        <v>582.378019652659</v>
+      </c>
+      <c r="F1658" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="str">
+        <v>R9</v>
+      </c>
+      <c r="B1659" t="str">
+        <v>12</v>
+      </c>
+      <c r="C1659" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1659" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1659">
+        <v>268.56888296037596</v>
+      </c>
+      <c r="F1659" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="str">
+        <v>R9</v>
+      </c>
+      <c r="B1660" t="str">
+        <v>15</v>
+      </c>
+      <c r="C1660" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1660" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1660">
+        <v>490.36679921976554</v>
+      </c>
+      <c r="F1660" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="str">
+        <v>R9</v>
+      </c>
+      <c r="B1661" t="str">
+        <v>16</v>
+      </c>
+      <c r="C1661" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1661" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1661">
+        <v>384.5973232636758</v>
+      </c>
+      <c r="F1661" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="str">
+        <v>R9</v>
+      </c>
+      <c r="B1662" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1662" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1662" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1662">
+        <v>512.463113131922</v>
+      </c>
+      <c r="F1662" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="str">
+        <v>R9</v>
+      </c>
+      <c r="B1663" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1663" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1663" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1663">
+        <v>158.4782813032848</v>
+      </c>
+      <c r="F1663" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="str">
+        <v>R9</v>
+      </c>
+      <c r="B1664" t="str">
+        <v>7</v>
+      </c>
+      <c r="C1664" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1664" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1664">
+        <v>166.38788857913738</v>
+      </c>
+      <c r="F1664" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="str">
+        <v>R9</v>
+      </c>
+      <c r="B1665" t="str">
+        <v>8</v>
+      </c>
+      <c r="C1665" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1665" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1665">
+        <v>790.999982128589</v>
+      </c>
+      <c r="F1665" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="str">
+        <v>R9</v>
+      </c>
+      <c r="B1666" t="str">
+        <v>OTH</v>
+      </c>
+      <c r="C1666" t="str">
+        <v>GVA</v>
+      </c>
+      <c r="D1666" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E1666">
+        <v>1087.5792173616437</v>
+      </c>
+      <c r="F1666" t="str">
+        <v>A</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1555"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1666"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/DATA/canonical/REGIONAL_GVA.xlsx
+++ b/DATA/canonical/REGIONAL_GVA.xlsx
@@ -474,7 +474,7 @@
         <v>vintage</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-26</v>
+        <v>2026-07-03</v>
       </c>
     </row>
   </sheetData>
@@ -997,7 +997,7 @@
         <v>2010</v>
       </c>
       <c r="E2">
-        <v>21821.56922225763</v>
+        <v>22148.65220205562</v>
       </c>
       <c r="F2" t="str">
         <v>A</v>
@@ -1017,7 +1017,7 @@
         <v>2011</v>
       </c>
       <c r="E3">
-        <v>25478.72443461741</v>
+        <v>26099.37533242154</v>
       </c>
       <c r="F3" t="str">
         <v>A</v>
@@ -1037,7 +1037,7 @@
         <v>2012</v>
       </c>
       <c r="E4">
-        <v>27227.328062034867</v>
+        <v>27896.854555001788</v>
       </c>
       <c r="F4" t="str">
         <v>A</v>
@@ -1057,7 +1057,7 @@
         <v>2013</v>
       </c>
       <c r="E5">
-        <v>28593.048837859333</v>
+        <v>29137.727778991604</v>
       </c>
       <c r="F5" t="str">
         <v>A</v>
@@ -1077,7 +1077,7 @@
         <v>2014</v>
       </c>
       <c r="E6">
-        <v>31124.095146338845</v>
+        <v>31722.398994712326</v>
       </c>
       <c r="F6" t="str">
         <v>A</v>
@@ -1097,7 +1097,7 @@
         <v>2015</v>
       </c>
       <c r="E7">
-        <v>33935.01558291179</v>
+        <v>34548.16243434734</v>
       </c>
       <c r="F7" t="str">
         <v>A</v>
@@ -1277,7 +1277,7 @@
         <v>2010</v>
       </c>
       <c r="E16">
-        <v>754.7422607796564</v>
+        <v>789.2537748065844</v>
       </c>
       <c r="F16" t="str">
         <v>A</v>
@@ -1297,7 +1297,7 @@
         <v>2011</v>
       </c>
       <c r="E17">
-        <v>814.8511128510027</v>
+        <v>862.1360634177769</v>
       </c>
       <c r="F17" t="str">
         <v>A</v>
@@ -1317,7 +1317,7 @@
         <v>2012</v>
       </c>
       <c r="E18">
-        <v>823.5284982459517</v>
+        <v>869.0807649860932</v>
       </c>
       <c r="F18" t="str">
         <v>A</v>
@@ -1337,7 +1337,7 @@
         <v>2013</v>
       </c>
       <c r="E19">
-        <v>1013.590104328231</v>
+        <v>1071.3643323180702</v>
       </c>
       <c r="F19" t="str">
         <v>A</v>
@@ -1357,7 +1357,7 @@
         <v>2014</v>
       </c>
       <c r="E20">
-        <v>1190.7261188599543</v>
+        <v>1263.0377937352066</v>
       </c>
       <c r="F20" t="str">
         <v>A</v>
@@ -1377,7 +1377,7 @@
         <v>2015</v>
       </c>
       <c r="E21">
-        <v>999.2719348659591</v>
+        <v>1042.0551056743125</v>
       </c>
       <c r="F21" t="str">
         <v>A</v>
@@ -1557,7 +1557,7 @@
         <v>2010</v>
       </c>
       <c r="E30">
-        <v>226.92039939731634</v>
+        <v>241.6377467300811</v>
       </c>
       <c r="F30" t="str">
         <v>A</v>
@@ -1577,7 +1577,7 @@
         <v>2011</v>
       </c>
       <c r="E31">
-        <v>275.459988021348</v>
+        <v>300.92519322695233</v>
       </c>
       <c r="F31" t="str">
         <v>A</v>
@@ -1597,7 +1597,7 @@
         <v>2012</v>
       </c>
       <c r="E32">
-        <v>222.71372281170648</v>
+        <v>239.08155676091133</v>
       </c>
       <c r="F32" t="str">
         <v>A</v>
@@ -1617,7 +1617,7 @@
         <v>2013</v>
       </c>
       <c r="E33">
-        <v>235.8442889214685</v>
+        <v>257.0249849163177</v>
       </c>
       <c r="F33" t="str">
         <v>A</v>
@@ -1637,7 +1637,7 @@
         <v>2014</v>
       </c>
       <c r="E34">
-        <v>278.3359864246761</v>
+        <v>306.24125129610337</v>
       </c>
       <c r="F34" t="str">
         <v>A</v>
@@ -1657,7 +1657,7 @@
         <v>2015</v>
       </c>
       <c r="E35">
-        <v>226.28190234394168</v>
+        <v>251.84244738896265</v>
       </c>
       <c r="F35" t="str">
         <v>A</v>
@@ -1837,7 +1837,7 @@
         <v>2010</v>
       </c>
       <c r="E44">
-        <v>100.73532508592335</v>
+        <v>100.22777282079721</v>
       </c>
       <c r="F44" t="str">
         <v>A</v>
@@ -1857,7 +1857,7 @@
         <v>2011</v>
       </c>
       <c r="E45">
-        <v>103.54523351668487</v>
+        <v>103.56641112444045</v>
       </c>
       <c r="F45" t="str">
         <v>A</v>
@@ -1877,7 +1877,7 @@
         <v>2012</v>
       </c>
       <c r="E46">
-        <v>104.71499220168853</v>
+        <v>104.81742864151319</v>
       </c>
       <c r="F46" t="str">
         <v>A</v>
@@ -1897,7 +1897,7 @@
         <v>2013</v>
       </c>
       <c r="E47">
-        <v>111.24859778324367</v>
+        <v>109.19812630590447</v>
       </c>
       <c r="F47" t="str">
         <v>A</v>
@@ -1917,7 +1917,7 @@
         <v>2014</v>
       </c>
       <c r="E48">
-        <v>118.56433823808312</v>
+        <v>117.35848277242744</v>
       </c>
       <c r="F48" t="str">
         <v>A</v>
@@ -1937,7 +1937,7 @@
         <v>2015</v>
       </c>
       <c r="E49">
-        <v>126.38155648633061</v>
+        <v>125.61554074271369</v>
       </c>
       <c r="F49" t="str">
         <v>A</v>
@@ -2117,7 +2117,7 @@
         <v>2010</v>
       </c>
       <c r="E58">
-        <v>68.07813127682456</v>
+        <v>73.45590897600401</v>
       </c>
       <c r="F58" t="str">
         <v>A</v>
@@ -2137,7 +2137,7 @@
         <v>2011</v>
       </c>
       <c r="E59">
-        <v>33.869889492552105</v>
+        <v>36.24661203966045</v>
       </c>
       <c r="F59" t="str">
         <v>A</v>
@@ -2157,7 +2157,7 @@
         <v>2012</v>
       </c>
       <c r="E60">
-        <v>70.30812176168857</v>
+        <v>72.9073710374342</v>
       </c>
       <c r="F60" t="str">
         <v>A</v>
@@ -2177,7 +2177,7 @@
         <v>2013</v>
       </c>
       <c r="E61">
-        <v>62.44249735231399</v>
+        <v>68.80025175608435</v>
       </c>
       <c r="F61" t="str">
         <v>A</v>
@@ -2197,7 +2197,7 @@
         <v>2014</v>
       </c>
       <c r="E62">
-        <v>91.15826042479262</v>
+        <v>100.6629213497774</v>
       </c>
       <c r="F62" t="str">
         <v>A</v>
@@ -2217,7 +2217,7 @@
         <v>2015</v>
       </c>
       <c r="E63">
-        <v>46.97055095048577</v>
+        <v>46.60911049387872</v>
       </c>
       <c r="F63" t="str">
         <v>A</v>
@@ -2397,7 +2397,7 @@
         <v>2010</v>
       </c>
       <c r="E72">
-        <v>47.29038946347013</v>
+        <v>44.10648649587233</v>
       </c>
       <c r="F72" t="str">
         <v>A</v>
@@ -2417,7 +2417,7 @@
         <v>2011</v>
       </c>
       <c r="E73">
-        <v>63.33996574205825</v>
+        <v>60.41995892768774</v>
       </c>
       <c r="F73" t="str">
         <v>A</v>
@@ -2437,7 +2437,7 @@
         <v>2012</v>
       </c>
       <c r="E74">
-        <v>53.54497128240389</v>
+        <v>56.67941613184777</v>
       </c>
       <c r="F74" t="str">
         <v>A</v>
@@ -2457,7 +2457,7 @@
         <v>2013</v>
       </c>
       <c r="E75">
-        <v>50.13999855738171</v>
+        <v>50.36608178035493</v>
       </c>
       <c r="F75" t="str">
         <v>A</v>
@@ -2477,7 +2477,7 @@
         <v>2014</v>
       </c>
       <c r="E76">
-        <v>72.85522646911978</v>
+        <v>72.44415624496317</v>
       </c>
       <c r="F76" t="str">
         <v>A</v>
@@ -2497,7 +2497,7 @@
         <v>2015</v>
       </c>
       <c r="E77">
-        <v>84.07421889314222</v>
+        <v>84.72496443115395</v>
       </c>
       <c r="F77" t="str">
         <v>A</v>
@@ -2677,7 +2677,7 @@
         <v>2010</v>
       </c>
       <c r="E86">
-        <v>52.89131381416044</v>
+        <v>88.10112745265401</v>
       </c>
       <c r="F86" t="str">
         <v>A</v>
@@ -2697,7 +2697,7 @@
         <v>2011</v>
       </c>
       <c r="E87">
-        <v>60.79536788714068</v>
+        <v>89.73071542725513</v>
       </c>
       <c r="F87" t="str">
         <v>A</v>
@@ -2717,7 +2717,7 @@
         <v>2012</v>
       </c>
       <c r="E88">
-        <v>97.09199574842428</v>
+        <v>144.6284133443389</v>
       </c>
       <c r="F88" t="str">
         <v>A</v>
@@ -2737,7 +2737,7 @@
         <v>2013</v>
       </c>
       <c r="E89">
-        <v>138.16956687476892</v>
+        <v>202.4937216315064</v>
       </c>
       <c r="F89" t="str">
         <v>A</v>
@@ -2757,7 +2757,7 @@
         <v>2014</v>
       </c>
       <c r="E90">
-        <v>185.7489403254642</v>
+        <v>266.64700479328957</v>
       </c>
       <c r="F90" t="str">
         <v>A</v>
@@ -2777,7 +2777,7 @@
         <v>2015</v>
       </c>
       <c r="E91">
-        <v>156.2695720421578</v>
+        <v>230.5714543678412</v>
       </c>
       <c r="F91" t="str">
         <v>A</v>
@@ -2957,7 +2957,7 @@
         <v>2010</v>
       </c>
       <c r="E100">
-        <v>20.183236000322793</v>
+        <v>21.364154569192127</v>
       </c>
       <c r="F100" t="str">
         <v>A</v>
@@ -2977,7 +2977,7 @@
         <v>2011</v>
       </c>
       <c r="E101">
-        <v>13.164488869483554</v>
+        <v>13.995002524597652</v>
       </c>
       <c r="F101" t="str">
         <v>A</v>
@@ -2997,7 +2997,7 @@
         <v>2012</v>
       </c>
       <c r="E102">
-        <v>21.211137105773137</v>
+        <v>20.00250581919505</v>
       </c>
       <c r="F102" t="str">
         <v>A</v>
@@ -3017,7 +3017,7 @@
         <v>2013</v>
       </c>
       <c r="E103">
-        <v>58.40927085518177</v>
+        <v>58.90846716870887</v>
       </c>
       <c r="F103" t="str">
         <v>A</v>
@@ -3037,7 +3037,7 @@
         <v>2014</v>
       </c>
       <c r="E104">
-        <v>24.997010734634287</v>
+        <v>25.695856157266423</v>
       </c>
       <c r="F104" t="str">
         <v>A</v>
@@ -3057,7 +3057,7 @@
         <v>2015</v>
       </c>
       <c r="E105">
-        <v>15.741601230649914</v>
+        <v>17.040325594431835</v>
       </c>
       <c r="F105" t="str">
         <v>A</v>
@@ -3237,7 +3237,7 @@
         <v>2010</v>
       </c>
       <c r="E114">
-        <v>32.670469995639436</v>
+        <v>31.894748345109612</v>
       </c>
       <c r="F114" t="str">
         <v>A</v>
@@ -3257,7 +3257,7 @@
         <v>2011</v>
       </c>
       <c r="E115">
-        <v>28.999829594612898</v>
+        <v>28.44697119981726</v>
       </c>
       <c r="F115" t="str">
         <v>A</v>
@@ -3277,7 +3277,7 @@
         <v>2012</v>
       </c>
       <c r="E116">
-        <v>31.136053944648285</v>
+        <v>30.249031162631237</v>
       </c>
       <c r="F116" t="str">
         <v>A</v>
@@ -3297,7 +3297,7 @@
         <v>2013</v>
       </c>
       <c r="E117">
-        <v>27.374651095345495</v>
+        <v>27.826237118811346</v>
       </c>
       <c r="F117" t="str">
         <v>A</v>
@@ -3317,7 +3317,7 @@
         <v>2014</v>
       </c>
       <c r="E118">
-        <v>31.558563862119946</v>
+        <v>31.255674896556233</v>
       </c>
       <c r="F118" t="str">
         <v>A</v>
@@ -3337,7 +3337,7 @@
         <v>2015</v>
       </c>
       <c r="E119">
-        <v>28.24963838476678</v>
+        <v>28.416524364336215</v>
       </c>
       <c r="F119" t="str">
         <v>A</v>
@@ -3517,7 +3517,7 @@
         <v>2010</v>
       </c>
       <c r="E128">
-        <v>0.9616925362598495</v>
+        <v>0.9961854437086276</v>
       </c>
       <c r="F128" t="str">
         <v>A</v>
@@ -3537,7 +3537,7 @@
         <v>2011</v>
       </c>
       <c r="E129">
-        <v>1.7184908508744965</v>
+        <v>1.843101998510246</v>
       </c>
       <c r="F129" t="str">
         <v>A</v>
@@ -3557,7 +3557,7 @@
         <v>2012</v>
       </c>
       <c r="E130">
-        <v>3.427372033483285</v>
+        <v>3.65961901229652</v>
       </c>
       <c r="F130" t="str">
         <v>A</v>
@@ -3577,7 +3577,7 @@
         <v>2013</v>
       </c>
       <c r="E131">
-        <v>4.459399408162285</v>
+        <v>4.47934699046631</v>
       </c>
       <c r="F131" t="str">
         <v>A</v>
@@ -3597,7 +3597,7 @@
         <v>2014</v>
       </c>
       <c r="E132">
-        <v>4.3650689790772335</v>
+        <v>4.397103078679851</v>
       </c>
       <c r="F132" t="str">
         <v>A</v>
@@ -3617,7 +3617,7 @@
         <v>2015</v>
       </c>
       <c r="E133">
-        <v>5.617674776236491</v>
+        <v>5.713225467305339</v>
       </c>
       <c r="F133" t="str">
         <v>A</v>
@@ -3797,7 +3797,7 @@
         <v>2010</v>
       </c>
       <c r="E142">
-        <v>117.3258721489027</v>
+        <v>94.25768994600352</v>
       </c>
       <c r="F142" t="str">
         <v>A</v>
@@ -3817,7 +3817,7 @@
         <v>2011</v>
       </c>
       <c r="E143">
-        <v>142.60069896861228</v>
+        <v>128.98551021441943</v>
       </c>
       <c r="F143" t="str">
         <v>A</v>
@@ -3837,7 +3837,7 @@
         <v>2012</v>
       </c>
       <c r="E144">
-        <v>129.37534547953032</v>
+        <v>100.41956853748172</v>
       </c>
       <c r="F144" t="str">
         <v>A</v>
@@ -3857,7 +3857,7 @@
         <v>2013</v>
       </c>
       <c r="E145">
-        <v>217.21077161663925</v>
+        <v>174.51374473433464</v>
       </c>
       <c r="F145" t="str">
         <v>A</v>
@@ -3877,7 +3877,7 @@
         <v>2014</v>
       </c>
       <c r="E146">
-        <v>250.66612967932065</v>
+        <v>193.39560564351518</v>
       </c>
       <c r="F146" t="str">
         <v>A</v>
@@ -3897,7 +3897,7 @@
         <v>2015</v>
       </c>
       <c r="E147">
-        <v>199.61741472828794</v>
+        <v>133.81110894753297</v>
       </c>
       <c r="F147" t="str">
         <v>A</v>
@@ -4077,7 +4077,7 @@
         <v>2010</v>
       </c>
       <c r="E156">
-        <v>1803.1169223666707</v>
+        <v>1876.71336814248</v>
       </c>
       <c r="F156" t="str">
         <v>A</v>
@@ -4097,7 +4097,7 @@
         <v>2011</v>
       </c>
       <c r="E157">
-        <v>2094.2355770660706</v>
+        <v>2152.7296438784906</v>
       </c>
       <c r="F157" t="str">
         <v>A</v>
@@ -4117,7 +4117,7 @@
         <v>2012</v>
       </c>
       <c r="E158">
-        <v>2035.959445743622</v>
+        <v>2104.9486399688203</v>
       </c>
       <c r="F158" t="str">
         <v>A</v>
@@ -4137,7 +4137,7 @@
         <v>2013</v>
       </c>
       <c r="E159">
-        <v>2018.844480931288</v>
+        <v>2074.560606600803</v>
       </c>
       <c r="F159" t="str">
         <v>A</v>
@@ -4157,7 +4157,7 @@
         <v>2014</v>
       </c>
       <c r="E160">
-        <v>2292.8724266909644</v>
+        <v>2328.0189812545545</v>
       </c>
       <c r="F160" t="str">
         <v>A</v>
@@ -4177,7 +4177,7 @@
         <v>2015</v>
       </c>
       <c r="E161">
-        <v>2356.418206751064</v>
+        <v>2416.390307545534</v>
       </c>
       <c r="F161" t="str">
         <v>A</v>
@@ -4357,7 +4357,7 @@
         <v>2010</v>
       </c>
       <c r="E170">
-        <v>342.8180663111583</v>
+        <v>365.05217380985926</v>
       </c>
       <c r="F170" t="str">
         <v>A</v>
@@ -4377,7 +4377,7 @@
         <v>2011</v>
       </c>
       <c r="E171">
-        <v>423.13463387325737</v>
+        <v>462.25178609046316</v>
       </c>
       <c r="F171" t="str">
         <v>A</v>
@@ -4397,7 +4397,7 @@
         <v>2012</v>
       </c>
       <c r="E172">
-        <v>377.9762051134389</v>
+        <v>405.7546988853645</v>
       </c>
       <c r="F172" t="str">
         <v>A</v>
@@ -4417,7 +4417,7 @@
         <v>2013</v>
       </c>
       <c r="E173">
-        <v>392.2151767535866</v>
+        <v>427.4392242019009</v>
       </c>
       <c r="F173" t="str">
         <v>A</v>
@@ -4437,7 +4437,7 @@
         <v>2014</v>
       </c>
       <c r="E174">
-        <v>410.3837469111301</v>
+        <v>451.5277876210187</v>
       </c>
       <c r="F174" t="str">
         <v>A</v>
@@ -4457,7 +4457,7 @@
         <v>2015</v>
       </c>
       <c r="E175">
-        <v>466.656085527783</v>
+        <v>519.3690235538027</v>
       </c>
       <c r="F175" t="str">
         <v>A</v>
@@ -4637,7 +4637,7 @@
         <v>2010</v>
       </c>
       <c r="E184">
-        <v>135.3231121394085</v>
+        <v>134.6412902260758</v>
       </c>
       <c r="F184" t="str">
         <v>A</v>
@@ -4657,7 +4657,7 @@
         <v>2011</v>
       </c>
       <c r="E185">
-        <v>139.03938508513724</v>
+        <v>139.06782214071097</v>
       </c>
       <c r="F185" t="str">
         <v>A</v>
@@ -4677,7 +4677,7 @@
         <v>2012</v>
       </c>
       <c r="E186">
-        <v>141.20338167662018</v>
+        <v>141.34151253454255</v>
       </c>
       <c r="F186" t="str">
         <v>A</v>
@@ -4697,7 +4697,7 @@
         <v>2013</v>
       </c>
       <c r="E187">
-        <v>150.50987517750076</v>
+        <v>147.73576195487252</v>
       </c>
       <c r="F187" t="str">
         <v>A</v>
@@ -4717,7 +4717,7 @@
         <v>2014</v>
       </c>
       <c r="E188">
-        <v>160.33042627134554</v>
+        <v>158.6997899121902</v>
       </c>
       <c r="F188" t="str">
         <v>A</v>
@@ -4737,7 +4737,7 @@
         <v>2015</v>
       </c>
       <c r="E189">
-        <v>170.9940069197963</v>
+        <v>169.95758906733164</v>
       </c>
       <c r="F189" t="str">
         <v>A</v>
@@ -4917,7 +4917,7 @@
         <v>2010</v>
       </c>
       <c r="E198">
-        <v>170.35558368344783</v>
+        <v>183.81268718616133</v>
       </c>
       <c r="F198" t="str">
         <v>A</v>
@@ -4937,7 +4937,7 @@
         <v>2011</v>
       </c>
       <c r="E199">
-        <v>146.68793976855682</v>
+        <v>156.98134606719452</v>
       </c>
       <c r="F199" t="str">
         <v>A</v>
@@ -4957,7 +4957,7 @@
         <v>2012</v>
       </c>
       <c r="E200">
-        <v>153.6886022402975</v>
+        <v>159.37037808715465</v>
       </c>
       <c r="F200" t="str">
         <v>A</v>
@@ -4977,7 +4977,7 @@
         <v>2013</v>
       </c>
       <c r="E201">
-        <v>226.82711308643806</v>
+        <v>249.9221387223142</v>
       </c>
       <c r="F201" t="str">
         <v>A</v>
@@ -4997,7 +4997,7 @@
         <v>2014</v>
       </c>
       <c r="E202">
-        <v>215.55338692300666</v>
+        <v>238.02816698559351</v>
       </c>
       <c r="F202" t="str">
         <v>A</v>
@@ -5017,7 +5017,7 @@
         <v>2015</v>
       </c>
       <c r="E203">
-        <v>220.76492825409125</v>
+        <v>219.06613241592666</v>
       </c>
       <c r="F203" t="str">
         <v>A</v>
@@ -5197,7 +5197,7 @@
         <v>2010</v>
       </c>
       <c r="E212">
-        <v>42.14624640058838</v>
+        <v>39.30868129464656</v>
       </c>
       <c r="F212" t="str">
         <v>A</v>
@@ -5217,7 +5217,7 @@
         <v>2011</v>
       </c>
       <c r="E213">
-        <v>45.95946656854578</v>
+        <v>43.840710203701775</v>
       </c>
       <c r="F213" t="str">
         <v>A</v>
@@ -5237,7 +5237,7 @@
         <v>2012</v>
       </c>
       <c r="E214">
-        <v>35.01831662413902</v>
+        <v>37.06823801824757</v>
       </c>
       <c r="F214" t="str">
         <v>A</v>
@@ -5257,7 +5257,7 @@
         <v>2013</v>
       </c>
       <c r="E215">
-        <v>55.305442111916335</v>
+        <v>55.5548165227734</v>
       </c>
       <c r="F215" t="str">
         <v>A</v>
@@ -5277,7 +5277,7 @@
         <v>2014</v>
       </c>
       <c r="E216">
-        <v>59.46115897357336</v>
+        <v>59.125661945666394</v>
       </c>
       <c r="F216" t="str">
         <v>A</v>
@@ -5297,7 +5297,7 @@
         <v>2015</v>
       </c>
       <c r="E217">
-        <v>70.77736465134446</v>
+        <v>71.32519078455697</v>
       </c>
       <c r="F217" t="str">
         <v>A</v>
@@ -5477,7 +5477,7 @@
         <v>2010</v>
       </c>
       <c r="E226">
-        <v>491.17781483559526</v>
+        <v>737.680837797301</v>
       </c>
       <c r="F226" t="str">
         <v>A</v>
@@ -5497,7 +5497,7 @@
         <v>2011</v>
       </c>
       <c r="E227">
-        <v>577.5008267174125</v>
+        <v>770.5906857997031</v>
       </c>
       <c r="F227" t="str">
         <v>A</v>
@@ -5517,7 +5517,7 @@
         <v>2012</v>
       </c>
       <c r="E228">
-        <v>586.7132474564552</v>
+        <v>801.3745241612452</v>
       </c>
       <c r="F228" t="str">
         <v>A</v>
@@ -5537,7 +5537,7 @@
         <v>2013</v>
       </c>
       <c r="E229">
-        <v>500.9720261190832</v>
+        <v>654.6793657468621</v>
       </c>
       <c r="F229" t="str">
         <v>A</v>
@@ -5557,7 +5557,7 @@
         <v>2014</v>
       </c>
       <c r="E230">
-        <v>530.7896581750199</v>
+        <v>656.8477063889753</v>
       </c>
       <c r="F230" t="str">
         <v>A</v>
@@ -5577,7 +5577,7 @@
         <v>2015</v>
       </c>
       <c r="E231">
-        <v>504.75587834578187</v>
+        <v>699.7906602167477</v>
       </c>
       <c r="F231" t="str">
         <v>A</v>
@@ -5757,7 +5757,7 @@
         <v>2010</v>
       </c>
       <c r="E240">
-        <v>27.253796382601486</v>
+        <v>28.848412539291285</v>
       </c>
       <c r="F240" t="str">
         <v>A</v>
@@ -5777,7 +5777,7 @@
         <v>2011</v>
       </c>
       <c r="E241">
-        <v>35.00557267567218</v>
+        <v>37.21398398586194</v>
       </c>
       <c r="F241" t="str">
         <v>A</v>
@@ -5797,7 +5797,7 @@
         <v>2012</v>
       </c>
       <c r="E242">
-        <v>52.97610828368706</v>
+        <v>49.95747794842862</v>
       </c>
       <c r="F242" t="str">
         <v>A</v>
@@ -5817,7 +5817,7 @@
         <v>2013</v>
       </c>
       <c r="E243">
-        <v>45.55114268627645</v>
+        <v>45.9404466815671</v>
       </c>
       <c r="F243" t="str">
         <v>A</v>
@@ -5837,7 +5837,7 @@
         <v>2014</v>
       </c>
       <c r="E244">
-        <v>76.46144460005782</v>
+        <v>78.59908942222671</v>
       </c>
       <c r="F244" t="str">
         <v>A</v>
@@ -5857,7 +5857,7 @@
         <v>2015</v>
       </c>
       <c r="E245">
-        <v>63.768524730530864</v>
+        <v>69.02959922330349</v>
       </c>
       <c r="F245" t="str">
         <v>A</v>
@@ -6037,7 +6037,7 @@
         <v>2010</v>
       </c>
       <c r="E254">
-        <v>46.26329327849672</v>
+        <v>45.16482612373186</v>
       </c>
       <c r="F254" t="str">
         <v>A</v>
@@ -6057,7 +6057,7 @@
         <v>2011</v>
       </c>
       <c r="E255">
-        <v>62.83296412166128</v>
+        <v>61.63510426627073</v>
       </c>
       <c r="F255" t="str">
         <v>A</v>
@@ -6077,7 +6077,7 @@
         <v>2012</v>
       </c>
       <c r="E256">
-        <v>93.40816183394485</v>
+        <v>90.7470934878937</v>
       </c>
       <c r="F256" t="str">
         <v>A</v>
@@ -6097,7 +6097,7 @@
         <v>2013</v>
       </c>
       <c r="E257">
-        <v>74.89815705782347</v>
+        <v>76.13371475654475</v>
       </c>
       <c r="F257" t="str">
         <v>A</v>
@@ -6117,7 +6117,7 @@
         <v>2014</v>
       </c>
       <c r="E258">
-        <v>112.49539790505689</v>
+        <v>111.41570318729313</v>
       </c>
       <c r="F258" t="str">
         <v>A</v>
@@ -6137,7 +6137,7 @@
         <v>2015</v>
       </c>
       <c r="E259">
-        <v>117.87803653279956</v>
+        <v>118.57440621118475</v>
       </c>
       <c r="F259" t="str">
         <v>A</v>
@@ -6317,7 +6317,7 @@
         <v>2010</v>
       </c>
       <c r="E268">
-        <v>9.269688807340062</v>
+        <v>9.602163591176964</v>
       </c>
       <c r="F268" t="str">
         <v>A</v>
@@ -6337,7 +6337,7 @@
         <v>2011</v>
       </c>
       <c r="E269">
-        <v>5.726459675192244</v>
+        <v>6.141696516082274</v>
       </c>
       <c r="F269" t="str">
         <v>A</v>
@@ -6357,7 +6357,7 @@
         <v>2012</v>
       </c>
       <c r="E270">
-        <v>14.895886145523509</v>
+        <v>15.90526724575026</v>
       </c>
       <c r="F270" t="str">
         <v>A</v>
@@ -6377,7 +6377,7 @@
         <v>2013</v>
       </c>
       <c r="E271">
-        <v>9.400896049639412</v>
+        <v>9.442947709631682</v>
       </c>
       <c r="F271" t="str">
         <v>A</v>
@@ -6397,7 +6397,7 @@
         <v>2014</v>
       </c>
       <c r="E272">
-        <v>8.486568535374005</v>
+        <v>8.548849242288304</v>
       </c>
       <c r="F272" t="str">
         <v>A</v>
@@ -6417,7 +6417,7 @@
         <v>2015</v>
       </c>
       <c r="E273">
-        <v>14.199394432961395</v>
+        <v>14.440911075499674</v>
       </c>
       <c r="F273" t="str">
         <v>A</v>
@@ -6597,7 +6597,7 @@
         <v>2010</v>
       </c>
       <c r="E282">
-        <v>329.0244502526043</v>
+        <v>110.95987107480823</v>
       </c>
       <c r="F282" t="str">
         <v>A</v>
@@ -6617,7 +6617,7 @@
         <v>2011</v>
       </c>
       <c r="E283">
-        <v>423.55277945402077</v>
+        <v>230.36171128882665</v>
       </c>
       <c r="F283" t="str">
         <v>A</v>
@@ -6637,7 +6637,7 @@
         <v>2012</v>
       </c>
       <c r="E284">
-        <v>357.5661754379812</v>
+        <v>169.3735151253626</v>
       </c>
       <c r="F284" t="str">
         <v>A</v>
@@ -6657,7 +6657,7 @@
         <v>2013</v>
       </c>
       <c r="E285">
-        <v>347.47310987000833</v>
+        <v>179.69778367125053</v>
       </c>
       <c r="F285" t="str">
         <v>A</v>
@@ -6677,7 +6677,7 @@
         <v>2014</v>
       </c>
       <c r="E286">
-        <v>463.8125733439035</v>
+        <v>298.0747115924108</v>
       </c>
       <c r="F286" t="str">
         <v>A</v>
@@ -6697,7 +6697,7 @@
         <v>2015</v>
       </c>
       <c r="E287">
-        <v>467.0692348405705</v>
+        <v>261.88167249475146</v>
       </c>
       <c r="F287" t="str">
         <v>A</v>
@@ -6877,7 +6877,7 @@
         <v>2010</v>
       </c>
       <c r="E296">
-        <v>871.0939694022676</v>
+        <v>909.5841352042706</v>
       </c>
       <c r="F296" t="str">
         <v>A</v>
@@ -6897,7 +6897,7 @@
         <v>2011</v>
       </c>
       <c r="E297">
-        <v>1106.5066065739709</v>
+        <v>1173.2543925850293</v>
       </c>
       <c r="F297" t="str">
         <v>A</v>
@@ -6917,7 +6917,7 @@
         <v>2012</v>
       </c>
       <c r="E298">
-        <v>1291.408626787792</v>
+        <v>1378.240386497366</v>
       </c>
       <c r="F298" t="str">
         <v>A</v>
@@ -6937,7 +6937,7 @@
         <v>2013</v>
       </c>
       <c r="E299">
-        <v>1436.3465093625227</v>
+        <v>1512.205345187138</v>
       </c>
       <c r="F299" t="str">
         <v>A</v>
@@ -6957,7 +6957,7 @@
         <v>2014</v>
       </c>
       <c r="E300">
-        <v>1622.3560248724068</v>
+        <v>1709.886241997544</v>
       </c>
       <c r="F300" t="str">
         <v>A</v>
@@ -6977,7 +6977,7 @@
         <v>2015</v>
       </c>
       <c r="E301">
-        <v>1583.225115284237</v>
+        <v>1635.1874176649096</v>
       </c>
       <c r="F301" t="str">
         <v>A</v>
@@ -7157,7 +7157,7 @@
         <v>2010</v>
       </c>
       <c r="E310">
-        <v>175.06393467943928</v>
+        <v>186.4180339096569</v>
       </c>
       <c r="F310" t="str">
         <v>A</v>
@@ -7177,7 +7177,7 @@
         <v>2011</v>
       </c>
       <c r="E311">
-        <v>193.74264939034992</v>
+        <v>211.65340426709943</v>
       </c>
       <c r="F311" t="str">
         <v>A</v>
@@ -7197,7 +7197,7 @@
         <v>2012</v>
       </c>
       <c r="E312">
-        <v>217.24587583880515</v>
+        <v>233.21186292297517</v>
       </c>
       <c r="F312" t="str">
         <v>A</v>
@@ -7217,7 +7217,7 @@
         <v>2013</v>
       </c>
       <c r="E313">
-        <v>234.27454309380664</v>
+        <v>255.31426340797714</v>
       </c>
       <c r="F313" t="str">
         <v>A</v>
@@ -7237,7 +7237,7 @@
         <v>2014</v>
       </c>
       <c r="E314">
-        <v>298.90563172797795</v>
+        <v>328.8731574226398</v>
       </c>
       <c r="F314" t="str">
         <v>A</v>
@@ -7257,7 +7257,7 @@
         <v>2015</v>
       </c>
       <c r="E315">
-        <v>253.15472143020764</v>
+        <v>281.75078940316104</v>
       </c>
       <c r="F315" t="str">
         <v>A</v>
@@ -7437,7 +7437,7 @@
         <v>2010</v>
       </c>
       <c r="E324">
-        <v>81.67691647209668</v>
+        <v>81.26538949356585</v>
       </c>
       <c r="F324" t="str">
         <v>A</v>
@@ -7457,7 +7457,7 @@
         <v>2011</v>
       </c>
       <c r="E325">
-        <v>83.75380807988658</v>
+        <v>83.77093784274781</v>
       </c>
       <c r="F325" t="str">
         <v>A</v>
@@ -7477,7 +7477,7 @@
         <v>2012</v>
       </c>
       <c r="E326">
-        <v>84.94192276754748</v>
+        <v>85.02501639127053</v>
       </c>
       <c r="F326" t="str">
         <v>A</v>
@@ -7497,7 +7497,7 @@
         <v>2013</v>
       </c>
       <c r="E327">
-        <v>90.45275317263196</v>
+        <v>88.7855789868624</v>
       </c>
       <c r="F327" t="str">
         <v>A</v>
@@ -7517,7 +7517,7 @@
         <v>2014</v>
       </c>
       <c r="E328">
-        <v>96.3351604515365</v>
+        <v>95.35538625052814</v>
       </c>
       <c r="F328" t="str">
         <v>A</v>
@@ -7537,7 +7537,7 @@
         <v>2015</v>
       </c>
       <c r="E329">
-        <v>102.4819422054164</v>
+        <v>101.86078526330928</v>
       </c>
       <c r="F329" t="str">
         <v>A</v>
@@ -7717,7 +7717,7 @@
         <v>2010</v>
       </c>
       <c r="E338">
-        <v>130.4576113924683</v>
+        <v>140.7630063860801</v>
       </c>
       <c r="F338" t="str">
         <v>A</v>
@@ -7737,7 +7737,7 @@
         <v>2011</v>
       </c>
       <c r="E339">
-        <v>194.47299725927525</v>
+        <v>208.1195831889842</v>
       </c>
       <c r="F339" t="str">
         <v>A</v>
@@ -7757,7 +7757,7 @@
         <v>2012</v>
       </c>
       <c r="E340">
-        <v>219.0472314264861</v>
+        <v>227.14527676425288</v>
       </c>
       <c r="F340" t="str">
         <v>A</v>
@@ -7777,7 +7777,7 @@
         <v>2013</v>
       </c>
       <c r="E341">
-        <v>203.4570741378711</v>
+        <v>224.17261505834244</v>
       </c>
       <c r="F341" t="str">
         <v>A</v>
@@ -7797,7 +7797,7 @@
         <v>2014</v>
       </c>
       <c r="E342">
-        <v>253.35923032072287</v>
+        <v>279.7758552671842</v>
       </c>
       <c r="F342" t="str">
         <v>A</v>
@@ -7817,7 +7817,7 @@
         <v>2015</v>
       </c>
       <c r="E343">
-        <v>216.04213236263251</v>
+        <v>214.3796786466898</v>
       </c>
       <c r="F343" t="str">
         <v>A</v>
@@ -7997,7 +7997,7 @@
         <v>2010</v>
       </c>
       <c r="E352">
-        <v>94.30178980306871</v>
+        <v>87.95276726783028</v>
       </c>
       <c r="F352" t="str">
         <v>A</v>
@@ -8017,7 +8017,7 @@
         <v>2011</v>
       </c>
       <c r="E353">
-        <v>88.43271640769744</v>
+        <v>84.3559201622535</v>
       </c>
       <c r="F353" t="str">
         <v>A</v>
@@ -8037,7 +8037,7 @@
         <v>2012</v>
       </c>
       <c r="E354">
-        <v>125.02149601123875</v>
+        <v>132.340072804854</v>
       </c>
       <c r="F354" t="str">
         <v>A</v>
@@ -8057,7 +8057,7 @@
         <v>2013</v>
       </c>
       <c r="E355">
-        <v>127.1024342249058</v>
+        <v>127.67554409335591</v>
       </c>
       <c r="F355" t="str">
         <v>A</v>
@@ -8077,7 +8077,7 @@
         <v>2014</v>
       </c>
       <c r="E356">
-        <v>123.23850606717659</v>
+        <v>122.54315883172146</v>
       </c>
       <c r="F356" t="str">
         <v>A</v>
@@ -8097,7 +8097,7 @@
         <v>2015</v>
       </c>
       <c r="E357">
-        <v>150.35218785509164</v>
+        <v>151.51593361050993</v>
       </c>
       <c r="F357" t="str">
         <v>A</v>
@@ -8277,7 +8277,7 @@
         <v>2010</v>
       </c>
       <c r="E366">
-        <v>61.34567586632644</v>
+        <v>102.44589493452924</v>
       </c>
       <c r="F366" t="str">
         <v>A</v>
@@ -8297,7 +8297,7 @@
         <v>2011</v>
       </c>
       <c r="E367">
-        <v>146.4164304650375</v>
+        <v>220.39863231198174</v>
       </c>
       <c r="F367" t="str">
         <v>A</v>
@@ -8317,7 +8317,7 @@
         <v>2012</v>
       </c>
       <c r="E368">
-        <v>100.83204140358089</v>
+        <v>159.39907763257176</v>
       </c>
       <c r="F368" t="str">
         <v>A</v>
@@ -8337,7 +8337,7 @@
         <v>2013</v>
       </c>
       <c r="E369">
-        <v>83.9362912843741</v>
+        <v>125.06296374993472</v>
       </c>
       <c r="F369" t="str">
         <v>A</v>
@@ -8357,7 +8357,7 @@
         <v>2014</v>
       </c>
       <c r="E370">
-        <v>117.06550112192055</v>
+        <v>170.02389659350894</v>
       </c>
       <c r="F370" t="str">
         <v>A</v>
@@ -8377,7 +8377,7 @@
         <v>2015</v>
       </c>
       <c r="E371">
-        <v>126.61212323240903</v>
+        <v>198.61706883774985</v>
       </c>
       <c r="F371" t="str">
         <v>A</v>
@@ -8557,7 +8557,7 @@
         <v>2010</v>
       </c>
       <c r="E380">
-        <v>32.65313340179612</v>
+        <v>34.56366408009427</v>
       </c>
       <c r="F380" t="str">
         <v>A</v>
@@ -8577,7 +8577,7 @@
         <v>2011</v>
       </c>
       <c r="E381">
-        <v>25.830322857547273</v>
+        <v>27.459891317202963</v>
       </c>
       <c r="F381" t="str">
         <v>A</v>
@@ -8597,7 +8597,7 @@
         <v>2012</v>
       </c>
       <c r="E382">
-        <v>32.489253908354954</v>
+        <v>30.637984523059735</v>
       </c>
       <c r="F382" t="str">
         <v>A</v>
@@ -8617,7 +8617,7 @@
         <v>2013</v>
       </c>
       <c r="E383">
-        <v>21.354200282225097</v>
+        <v>21.53670449607903</v>
       </c>
       <c r="F383" t="str">
         <v>A</v>
@@ -8637,7 +8637,7 @@
         <v>2014</v>
       </c>
       <c r="E384">
-        <v>29.530782289445412</v>
+        <v>30.356379087751026</v>
       </c>
       <c r="F384" t="str">
         <v>A</v>
@@ -8657,7 +8657,7 @@
         <v>2015</v>
       </c>
       <c r="E385">
-        <v>24.063594237936176</v>
+        <v>26.048905367284334</v>
       </c>
       <c r="F385" t="str">
         <v>A</v>
@@ -8837,7 +8837,7 @@
         <v>2010</v>
       </c>
       <c r="E394">
-        <v>18.839176128872378</v>
+        <v>18.391862184406275</v>
       </c>
       <c r="F394" t="str">
         <v>A</v>
@@ -8857,7 +8857,7 @@
         <v>2011</v>
       </c>
       <c r="E395">
-        <v>36.73311748650967</v>
+        <v>36.0328301864352</v>
       </c>
       <c r="F395" t="str">
         <v>A</v>
@@ -8877,7 +8877,7 @@
         <v>2012</v>
       </c>
       <c r="E396">
-        <v>53.56046585297011</v>
+        <v>52.03460282898223</v>
       </c>
       <c r="F396" t="str">
         <v>A</v>
@@ -8897,7 +8897,7 @@
         <v>2013</v>
       </c>
       <c r="E397">
-        <v>41.82624355177155</v>
+        <v>42.516230318589926</v>
       </c>
       <c r="F397" t="str">
         <v>A</v>
@@ -8917,7 +8917,7 @@
         <v>2014</v>
       </c>
       <c r="E398">
-        <v>51.28266627594492</v>
+        <v>50.79047170690389</v>
       </c>
       <c r="F398" t="str">
         <v>A</v>
@@ -8937,7 +8937,7 @@
         <v>2015</v>
       </c>
       <c r="E399">
-        <v>54.316350167074305</v>
+        <v>54.637226391428264</v>
       </c>
       <c r="F399" t="str">
         <v>A</v>
@@ -9117,7 +9117,7 @@
         <v>2010</v>
       </c>
       <c r="E408">
-        <v>2.26327418693937</v>
+        <v>2.3444507627345</v>
       </c>
       <c r="F408" t="str">
         <v>A</v>
@@ -9137,7 +9137,7 @@
         <v>2011</v>
       </c>
       <c r="E409">
-        <v>7.833132330778641</v>
+        <v>8.401128144561595</v>
       </c>
       <c r="F409" t="str">
         <v>A</v>
@@ -9157,7 +9157,7 @@
         <v>2012</v>
       </c>
       <c r="E410">
-        <v>3.6910160360589224</v>
+        <v>3.9411281670885594</v>
       </c>
       <c r="F410" t="str">
         <v>A</v>
@@ -9177,7 +9177,7 @@
         <v>2013</v>
       </c>
       <c r="E411">
-        <v>5.6646424914493885</v>
+        <v>5.689981312213962</v>
       </c>
       <c r="F411" t="str">
         <v>A</v>
@@ -9197,7 +9197,7 @@
         <v>2014</v>
       </c>
       <c r="E412">
-        <v>7.26921323252223</v>
+        <v>7.322560087254525</v>
       </c>
       <c r="F412" t="str">
         <v>A</v>
@@ -9217,7 +9217,7 @@
         <v>2015</v>
       </c>
       <c r="E413">
-        <v>4.503224570916847</v>
+        <v>4.5798196457349</v>
       </c>
       <c r="F413" t="str">
         <v>A</v>
@@ -9397,7 +9397,7 @@
         <v>2010</v>
       </c>
       <c r="E422">
-        <v>173.28936580572997</v>
+        <v>148.0159314461402</v>
       </c>
       <c r="F422" t="str">
         <v>A</v>
@@ -9417,7 +9417,7 @@
         <v>2011</v>
       </c>
       <c r="E423">
-        <v>205.23527111432725</v>
+        <v>159.72874849335093</v>
       </c>
       <c r="F423" t="str">
         <v>A</v>
@@ -9437,7 +9437,7 @@
         <v>2012</v>
       </c>
       <c r="E424">
-        <v>313.4391478465807</v>
+        <v>301.25443212727265</v>
       </c>
       <c r="F424" t="str">
         <v>A</v>
@@ -9457,7 +9457,7 @@
         <v>2013</v>
       </c>
       <c r="E425">
-        <v>474.82034836173557</v>
+        <v>455.24537492109823</v>
       </c>
       <c r="F425" t="str">
         <v>A</v>
@@ -9477,7 +9477,7 @@
         <v>2014</v>
       </c>
       <c r="E426">
-        <v>464.8708992143212</v>
+        <v>428.6276037714898</v>
       </c>
       <c r="F426" t="str">
         <v>A</v>
@@ -9497,7 +9497,7 @@
         <v>2015</v>
       </c>
       <c r="E427">
-        <v>477.30975930606644</v>
+        <v>417.0866608376669</v>
       </c>
       <c r="F427" t="str">
         <v>A</v>
@@ -9677,7 +9677,7 @@
         <v>2010</v>
       </c>
       <c r="E436">
-        <v>11683.948100266764</v>
+        <v>11706.849619936398</v>
       </c>
       <c r="F436" t="str">
         <v>A</v>
@@ -9697,7 +9697,7 @@
         <v>2011</v>
       </c>
       <c r="E437">
-        <v>13741.007877083694</v>
+        <v>13901.747429705621</v>
       </c>
       <c r="F437" t="str">
         <v>A</v>
@@ -9717,7 +9717,7 @@
         <v>2012</v>
       </c>
       <c r="E438">
-        <v>14393.59945095776</v>
+        <v>14482.609439900023</v>
       </c>
       <c r="F438" t="str">
         <v>A</v>
@@ -9737,7 +9737,7 @@
         <v>2013</v>
       </c>
       <c r="E439">
-        <v>14658.277956080256</v>
+        <v>14750.853329607351</v>
       </c>
       <c r="F439" t="str">
         <v>A</v>
@@ -9757,7 +9757,7 @@
         <v>2014</v>
       </c>
       <c r="E440">
-        <v>15930.136026019789</v>
+        <v>15990.36151559449</v>
       </c>
       <c r="F440" t="str">
         <v>A</v>
@@ -9777,7 +9777,7 @@
         <v>2015</v>
       </c>
       <c r="E441">
-        <v>17317.714707993113</v>
+        <v>17425.358714915244</v>
       </c>
       <c r="F441" t="str">
         <v>A</v>
@@ -9957,7 +9957,7 @@
         <v>2010</v>
       </c>
       <c r="E450">
-        <v>31.285134943776225</v>
+        <v>33.31419094113411</v>
       </c>
       <c r="F450" t="str">
         <v>A</v>
@@ -9977,7 +9977,7 @@
         <v>2011</v>
       </c>
       <c r="E451">
-        <v>38.614721395969</v>
+        <v>42.1845022972496</v>
       </c>
       <c r="F451" t="str">
         <v>A</v>
@@ -9997,7 +9997,7 @@
         <v>2012</v>
       </c>
       <c r="E452">
-        <v>34.49362138276984</v>
+        <v>37.028650926401724</v>
       </c>
       <c r="F452" t="str">
         <v>A</v>
@@ -10017,7 +10017,7 @@
         <v>2013</v>
       </c>
       <c r="E453">
-        <v>35.7930515849643</v>
+        <v>39.007552762058836</v>
       </c>
       <c r="F453" t="str">
         <v>A</v>
@@ -10037,7 +10037,7 @@
         <v>2014</v>
       </c>
       <c r="E454">
-        <v>45.042747547713994</v>
+        <v>49.558619954302515</v>
       </c>
       <c r="F454" t="str">
         <v>A</v>
@@ -10057,7 +10057,7 @@
         <v>2015</v>
       </c>
       <c r="E455">
-        <v>45.59642247763814</v>
+        <v>50.746942243288686</v>
       </c>
       <c r="F455" t="str">
         <v>A</v>
@@ -10237,7 +10237,7 @@
         <v>2010</v>
       </c>
       <c r="E464">
-        <v>1314.8748930140493</v>
+        <v>1308.249930720658</v>
       </c>
       <c r="F464" t="str">
         <v>A</v>
@@ -10257,7 +10257,7 @@
         <v>2011</v>
       </c>
       <c r="E465">
-        <v>1367.9349760378816</v>
+        <v>1368.2147531881546</v>
       </c>
       <c r="F465" t="str">
         <v>A</v>
@@ -10277,7 +10277,7 @@
         <v>2012</v>
       </c>
       <c r="E466">
-        <v>1421.0843354798596</v>
+        <v>1422.4744976424731</v>
       </c>
       <c r="F466" t="str">
         <v>A</v>
@@ -10297,7 +10297,7 @@
         <v>2013</v>
       </c>
       <c r="E467">
-        <v>1591.0811591313436</v>
+        <v>1561.7552476148032</v>
       </c>
       <c r="F467" t="str">
         <v>A</v>
@@ -10317,7 +10317,7 @@
         <v>2014</v>
       </c>
       <c r="E468">
-        <v>1765.6460829283728</v>
+        <v>1747.688626148769</v>
       </c>
       <c r="F468" t="str">
         <v>A</v>
@@ -10337,7 +10337,7 @@
         <v>2015</v>
       </c>
       <c r="E469">
-        <v>1935.3572158395723</v>
+        <v>1923.626753436096</v>
       </c>
       <c r="F469" t="str">
         <v>A</v>
@@ -10517,7 +10517,7 @@
         <v>2010</v>
       </c>
       <c r="E478">
-        <v>682.7779618130239</v>
+        <v>736.7134625041137</v>
       </c>
       <c r="F478" t="str">
         <v>A</v>
@@ -10537,7 +10537,7 @@
         <v>2011</v>
       </c>
       <c r="E479">
-        <v>751.358747922098</v>
+        <v>804.0831973935447</v>
       </c>
       <c r="F479" t="str">
         <v>A</v>
@@ -10557,7 +10557,7 @@
         <v>2012</v>
       </c>
       <c r="E480">
-        <v>837.585583754223</v>
+        <v>868.5506226060284</v>
       </c>
       <c r="F480" t="str">
         <v>A</v>
@@ -10577,7 +10577,7 @@
         <v>2013</v>
       </c>
       <c r="E481">
-        <v>878.754092608611</v>
+        <v>968.2268545737695</v>
       </c>
       <c r="F481" t="str">
         <v>A</v>
@@ -10597,7 +10597,7 @@
         <v>2014</v>
       </c>
       <c r="E482">
-        <v>965.0357261559208</v>
+        <v>1065.655651490892</v>
       </c>
       <c r="F482" t="str">
         <v>A</v>
@@ -10617,7 +10617,7 @@
         <v>2015</v>
       </c>
       <c r="E483">
-        <v>1198.7897690713426</v>
+        <v>1189.5650290429412</v>
       </c>
       <c r="F483" t="str">
         <v>A</v>
@@ -10797,7 +10797,7 @@
         <v>2010</v>
       </c>
       <c r="E492">
-        <v>291.0928813914164</v>
+        <v>271.49457612424055</v>
       </c>
       <c r="F492" t="str">
         <v>A</v>
@@ -10817,7 +10817,7 @@
         <v>2011</v>
       </c>
       <c r="E493">
-        <v>323.21360650027026</v>
+        <v>308.31328373531215</v>
       </c>
       <c r="F493" t="str">
         <v>A</v>
@@ -10837,7 +10837,7 @@
         <v>2012</v>
       </c>
       <c r="E494">
-        <v>319.3449261926266</v>
+        <v>338.03891435112723</v>
       </c>
       <c r="F494" t="str">
         <v>A</v>
@@ -10857,7 +10857,7 @@
         <v>2013</v>
       </c>
       <c r="E495">
-        <v>409.4184381130034</v>
+        <v>411.26452193223844</v>
       </c>
       <c r="F495" t="str">
         <v>A</v>
@@ -10877,7 +10877,7 @@
         <v>2014</v>
       </c>
       <c r="E496">
-        <v>443.6516761673407</v>
+        <v>441.14846530920323</v>
       </c>
       <c r="F496" t="str">
         <v>A</v>
@@ -10897,7 +10897,7 @@
         <v>2015</v>
       </c>
       <c r="E497">
-        <v>401.4968239243452</v>
+        <v>404.604462272157</v>
       </c>
       <c r="F497" t="str">
         <v>A</v>
@@ -11077,7 +11077,7 @@
         <v>2010</v>
       </c>
       <c r="E506">
-        <v>923.2781972822745</v>
+        <v>1251.1770647875364</v>
       </c>
       <c r="F506" t="str">
         <v>A</v>
@@ -11097,7 +11097,7 @@
         <v>2011</v>
       </c>
       <c r="E507">
-        <v>1136.5754711532416</v>
+        <v>1474.9814319174875</v>
       </c>
       <c r="F507" t="str">
         <v>A</v>
@@ -11117,7 +11117,7 @@
         <v>2012</v>
       </c>
       <c r="E508">
-        <v>1096.3130110728246</v>
+        <v>1462.8260730749516</v>
       </c>
       <c r="F508" t="str">
         <v>A</v>
@@ -11137,7 +11137,7 @@
         <v>2013</v>
       </c>
       <c r="E509">
-        <v>1269.2063867484756</v>
+        <v>1605.2048184525668</v>
       </c>
       <c r="F509" t="str">
         <v>A</v>
@@ -11157,7 +11157,7 @@
         <v>2014</v>
       </c>
       <c r="E510">
-        <v>1313.4964954570646</v>
+        <v>1622.5995229806854</v>
       </c>
       <c r="F510" t="str">
         <v>A</v>
@@ -11177,7 +11177,7 @@
         <v>2015</v>
       </c>
       <c r="E511">
-        <v>1230.2112542531288</v>
+        <v>1719.0325988972318</v>
       </c>
       <c r="F511" t="str">
         <v>A</v>
@@ -11357,7 +11357,7 @@
         <v>2010</v>
       </c>
       <c r="E520">
-        <v>533.5059197537555</v>
+        <v>564.7212831983907</v>
       </c>
       <c r="F520" t="str">
         <v>A</v>
@@ -11377,7 +11377,7 @@
         <v>2011</v>
       </c>
       <c r="E521">
-        <v>858.2847818998141</v>
+        <v>912.4317555052075</v>
       </c>
       <c r="F521" t="str">
         <v>A</v>
@@ -11397,7 +11397,7 @@
         <v>2012</v>
       </c>
       <c r="E522">
-        <v>1314.8835626349514</v>
+        <v>1239.960214391857</v>
       </c>
       <c r="F522" t="str">
         <v>A</v>
@@ -11417,7 +11417,7 @@
         <v>2013</v>
       </c>
       <c r="E523">
-        <v>1058.0699651600123</v>
+        <v>1067.1127869300562</v>
       </c>
       <c r="F523" t="str">
         <v>A</v>
@@ -11437,7 +11437,7 @@
         <v>2014</v>
       </c>
       <c r="E524">
-        <v>1168.3651831114605</v>
+        <v>1201.029355193801</v>
       </c>
       <c r="F524" t="str">
         <v>A</v>
@@ -11457,7 +11457,7 @@
         <v>2015</v>
       </c>
       <c r="E525">
-        <v>1594.5139131912458</v>
+        <v>1726.065591899678</v>
       </c>
       <c r="F525" t="str">
         <v>A</v>
@@ -11637,7 +11637,7 @@
         <v>2010</v>
       </c>
       <c r="E534">
-        <v>2962.7585344950685</v>
+        <v>2892.411338975488</v>
       </c>
       <c r="F534" t="str">
         <v>A</v>
@@ -11657,7 +11657,7 @@
         <v>2011</v>
       </c>
       <c r="E535">
-        <v>3484.039527496793</v>
+        <v>3417.6191199460454</v>
       </c>
       <c r="F535" t="str">
         <v>A</v>
@@ -11677,7 +11677,7 @@
         <v>2012</v>
       </c>
       <c r="E536">
-        <v>3319.458269249135</v>
+        <v>3224.891529545597</v>
       </c>
       <c r="F536" t="str">
         <v>A</v>
@@ -11697,7 +11697,7 @@
         <v>2013</v>
       </c>
       <c r="E537">
-        <v>3170.0401798889184</v>
+        <v>3222.3347583321993</v>
       </c>
       <c r="F537" t="str">
         <v>A</v>
@@ -11717,7 +11717,7 @@
         <v>2014</v>
       </c>
       <c r="E538">
-        <v>3289.7082260409866</v>
+        <v>3258.1346624927414</v>
       </c>
       <c r="F538" t="str">
         <v>A</v>
@@ -11737,7 +11737,7 @@
         <v>2015</v>
       </c>
       <c r="E539">
-        <v>3283.5068324403237</v>
+        <v>3302.904293274733</v>
       </c>
       <c r="F539" t="str">
         <v>A</v>
@@ -11917,7 +11917,7 @@
         <v>2010</v>
       </c>
       <c r="E548">
-        <v>960.554750058154</v>
+        <v>995.0068486697292</v>
       </c>
       <c r="F548" t="str">
         <v>A</v>
@@ -11937,7 +11937,7 @@
         <v>2011</v>
       </c>
       <c r="E549">
-        <v>1137.9846777079977</v>
+        <v>1220.5021823015952</v>
       </c>
       <c r="F549" t="str">
         <v>A</v>
@@ -11957,7 +11957,7 @@
         <v>2012</v>
       </c>
       <c r="E550">
-        <v>1220.408087922625</v>
+        <v>1303.105877532353</v>
       </c>
       <c r="F550" t="str">
         <v>A</v>
@@ -11977,7 +11977,7 @@
         <v>2013</v>
       </c>
       <c r="E551">
-        <v>1201.506829728914</v>
+        <v>1206.8813553502337</v>
       </c>
       <c r="F551" t="str">
         <v>A</v>
@@ -11997,7 +11997,7 @@
         <v>2014</v>
       </c>
       <c r="E552">
-        <v>1246.4812139341548</v>
+        <v>1255.6288135600373</v>
       </c>
       <c r="F552" t="str">
         <v>A</v>
@@ -12017,7 +12017,7 @@
         <v>2015</v>
       </c>
       <c r="E553">
-        <v>1262.5478933986046</v>
+        <v>1284.0224942836658</v>
       </c>
       <c r="F553" t="str">
         <v>A</v>
@@ -12197,7 +12197,7 @@
         <v>2010</v>
       </c>
       <c r="E562">
-        <v>2626.386861450772</v>
+        <v>2271.1659166693107</v>
       </c>
       <c r="F562" t="str">
         <v>A</v>
@@ -12217,7 +12217,7 @@
         <v>2011</v>
       </c>
       <c r="E563">
-        <v>3102.4261206198626</v>
+        <v>2773.567083931532</v>
       </c>
       <c r="F563" t="str">
         <v>A</v>
@@ -12237,7 +12237,7 @@
         <v>2012</v>
       </c>
       <c r="E564">
-        <v>3256.9278638565193</v>
+        <v>2975.3656514633885</v>
       </c>
       <c r="F564" t="str">
         <v>A</v>
@@ -12257,7 +12257,7 @@
         <v>2013</v>
       </c>
       <c r="E565">
-        <v>3478.330522468026</v>
+        <v>3047.803052324091</v>
       </c>
       <c r="F565" t="str">
         <v>A</v>
@@ -12277,7 +12277,7 @@
         <v>2014</v>
       </c>
       <c r="E566">
-        <v>3920.369826271919</v>
+        <v>3513.945945572477</v>
       </c>
       <c r="F566" t="str">
         <v>A</v>
@@ -12297,7 +12297,7 @@
         <v>2015</v>
       </c>
       <c r="E567">
-        <v>4458.182944636095</v>
+        <v>3856.424384618473</v>
       </c>
       <c r="F567" t="str">
         <v>A</v>
@@ -12477,7 +12477,7 @@
         <v>2010</v>
       </c>
       <c r="E576">
-        <v>1565.8479098819878</v>
+        <v>1592.8542182409578</v>
       </c>
       <c r="F576" t="str">
         <v>A</v>
@@ -12497,7 +12497,7 @@
         <v>2011</v>
       </c>
       <c r="E577">
-        <v>1883.5779569937924</v>
+        <v>1929.910741548543</v>
       </c>
       <c r="F577" t="str">
         <v>A</v>
@@ -12517,7 +12517,7 @@
         <v>2012</v>
       </c>
       <c r="E578">
-        <v>2410.8220333489544</v>
+        <v>2501.544282135232</v>
       </c>
       <c r="F578" t="str">
         <v>A</v>
@@ -12537,7 +12537,7 @@
         <v>2013</v>
       </c>
       <c r="E579">
-        <v>2461.7212314177314</v>
+        <v>2507.897873660046</v>
       </c>
       <c r="F579" t="str">
         <v>A</v>
@@ -12557,7 +12557,7 @@
         <v>2014</v>
       </c>
       <c r="E580">
-        <v>2568.185088634663</v>
+        <v>2626.5419129262145</v>
       </c>
       <c r="F580" t="str">
         <v>A</v>
@@ -12577,7 +12577,7 @@
         <v>2015</v>
       </c>
       <c r="E581">
-        <v>3119.329799098965</v>
+        <v>3174.5242304809203</v>
       </c>
       <c r="F581" t="str">
         <v>A</v>
@@ -12757,7 +12757,7 @@
         <v>2010</v>
       </c>
       <c r="E590">
-        <v>89.65664304908161</v>
+        <v>95.47149248504046</v>
       </c>
       <c r="F590" t="str">
         <v>A</v>
@@ -12777,7 +12777,7 @@
         <v>2011</v>
       </c>
       <c r="E591">
-        <v>115.95082975112814</v>
+        <v>126.67003327169076</v>
       </c>
       <c r="F591" t="str">
         <v>A</v>
@@ -12797,7 +12797,7 @@
         <v>2012</v>
       </c>
       <c r="E592">
-        <v>135.580383575831</v>
+        <v>145.54455272141567</v>
       </c>
       <c r="F592" t="str">
         <v>A</v>
@@ -12817,7 +12817,7 @@
         <v>2013</v>
       </c>
       <c r="E593">
-        <v>149.53915187548046</v>
+        <v>162.96895901512588</v>
       </c>
       <c r="F593" t="str">
         <v>A</v>
@@ -12837,7 +12837,7 @@
         <v>2014</v>
       </c>
       <c r="E594">
-        <v>134.50537391752076</v>
+        <v>147.99054388785999</v>
       </c>
       <c r="F594" t="str">
         <v>A</v>
@@ -12857,7 +12857,7 @@
         <v>2015</v>
       </c>
       <c r="E595">
-        <v>142.53783714786013</v>
+        <v>158.638748309107</v>
       </c>
       <c r="F595" t="str">
         <v>A</v>
@@ -13037,7 +13037,7 @@
         <v>2010</v>
       </c>
       <c r="E604">
-        <v>338.45098585060964</v>
+        <v>336.74570953015177</v>
       </c>
       <c r="F604" t="str">
         <v>A</v>
@@ -13057,7 +13057,7 @@
         <v>2011</v>
       </c>
       <c r="E605">
-        <v>349.65377015640854</v>
+        <v>349.7252831574724</v>
       </c>
       <c r="F605" t="str">
         <v>A</v>
@@ -13077,7 +13077,7 @@
         <v>2012</v>
       </c>
       <c r="E606">
-        <v>360.37201532314754</v>
+        <v>360.7245458012193</v>
       </c>
       <c r="F606" t="str">
         <v>A</v>
@@ -13097,7 +13097,7 @@
         <v>2013</v>
       </c>
       <c r="E607">
-        <v>392.5223840541856</v>
+        <v>385.2876326167925</v>
       </c>
       <c r="F607" t="str">
         <v>A</v>
@@ -13117,7 +13117,7 @@
         <v>2014</v>
       </c>
       <c r="E608">
-        <v>423.85689011243187</v>
+        <v>419.5460648238736</v>
       </c>
       <c r="F608" t="str">
         <v>A</v>
@@ -13137,7 +13137,7 @@
         <v>2015</v>
       </c>
       <c r="E609">
-        <v>458.36869986816754</v>
+        <v>455.5904650509835</v>
       </c>
       <c r="F609" t="str">
         <v>A</v>
@@ -13317,7 +13317,7 @@
         <v>2010</v>
       </c>
       <c r="E618">
-        <v>151.6259675050821</v>
+        <v>163.6035399115521</v>
       </c>
       <c r="F618" t="str">
         <v>A</v>
@@ -13337,7 +13337,7 @@
         <v>2011</v>
       </c>
       <c r="E619">
-        <v>200.87384701795784</v>
+        <v>214.96959425790547</v>
       </c>
       <c r="F619" t="str">
         <v>A</v>
@@ -13357,7 +13357,7 @@
         <v>2012</v>
       </c>
       <c r="E620">
-        <v>140.46569131814098</v>
+        <v>145.6586240445097</v>
       </c>
       <c r="F620" t="str">
         <v>A</v>
@@ -13377,7 +13377,7 @@
         <v>2013</v>
       </c>
       <c r="E621">
-        <v>195.36999193875573</v>
+        <v>215.26212436909285</v>
       </c>
       <c r="F621" t="str">
         <v>A</v>
@@ -13397,7 +13397,7 @@
         <v>2014</v>
       </c>
       <c r="E622">
-        <v>152.98066752131103</v>
+        <v>168.93127217405666</v>
       </c>
       <c r="F622" t="str">
         <v>A</v>
@@ -13417,7 +13417,7 @@
         <v>2015</v>
       </c>
       <c r="E623">
-        <v>223.12760625564792</v>
+        <v>221.4106295062865</v>
       </c>
       <c r="F623" t="str">
         <v>A</v>
@@ -13597,7 +13597,7 @@
         <v>2010</v>
       </c>
       <c r="E632">
-        <v>84.90238490901932</v>
+        <v>79.18619271151651</v>
       </c>
       <c r="F632" t="str">
         <v>A</v>
@@ -13617,7 +13617,7 @@
         <v>2011</v>
       </c>
       <c r="E633">
-        <v>107.49709093129047</v>
+        <v>102.5414166683354</v>
       </c>
       <c r="F633" t="str">
         <v>A</v>
@@ -13637,7 +13637,7 @@
         <v>2012</v>
       </c>
       <c r="E634">
-        <v>142.4185904288659</v>
+        <v>150.75556786191785</v>
       </c>
       <c r="F634" t="str">
         <v>A</v>
@@ -13657,7 +13657,7 @@
         <v>2013</v>
       </c>
       <c r="E635">
-        <v>120.81533108884354</v>
+        <v>121.36009216229836</v>
       </c>
       <c r="F635" t="str">
         <v>A</v>
@@ -13677,7 +13677,7 @@
         <v>2014</v>
       </c>
       <c r="E636">
-        <v>160.7969937440561</v>
+        <v>159.8897306763873</v>
       </c>
       <c r="F636" t="str">
         <v>A</v>
@@ -13697,7 +13697,7 @@
         <v>2015</v>
       </c>
       <c r="E637">
-        <v>191.98115470378755</v>
+        <v>193.4671141506974</v>
       </c>
       <c r="F637" t="str">
         <v>A</v>
@@ -13877,7 +13877,7 @@
         <v>2010</v>
       </c>
       <c r="E646">
-        <v>59.48984029389977</v>
+        <v>98.7983847903835</v>
       </c>
       <c r="F646" t="str">
         <v>A</v>
@@ -13897,7 +13897,7 @@
         <v>2011</v>
       </c>
       <c r="E647">
-        <v>76.57347606837683</v>
+        <v>109.73219611107412</v>
       </c>
       <c r="F647" t="str">
         <v>A</v>
@@ -13917,7 +13917,7 @@
         <v>2012</v>
       </c>
       <c r="E648">
-        <v>90.58926607323377</v>
+        <v>143.041168046523</v>
       </c>
       <c r="F648" t="str">
         <v>A</v>
@@ -13937,7 +13937,7 @@
         <v>2013</v>
       </c>
       <c r="E649">
-        <v>101.36501839231812</v>
+        <v>147.42276671071508</v>
       </c>
       <c r="F649" t="str">
         <v>A</v>
@@ -13957,7 +13957,7 @@
         <v>2014</v>
       </c>
       <c r="E650">
-        <v>112.69906524964905</v>
+        <v>156.60888927384877</v>
       </c>
       <c r="F650" t="str">
         <v>A</v>
@@ -13977,7 +13977,7 @@
         <v>2015</v>
       </c>
       <c r="E651">
-        <v>131.40848592432192</v>
+        <v>202.59872515761495</v>
       </c>
       <c r="F651" t="str">
         <v>A</v>
@@ -14157,7 +14157,7 @@
         <v>2010</v>
       </c>
       <c r="E660">
-        <v>109.27229681703425</v>
+        <v>115.66580499244145</v>
       </c>
       <c r="F660" t="str">
         <v>A</v>
@@ -14177,7 +14177,7 @@
         <v>2011</v>
       </c>
       <c r="E661">
-        <v>116.98443518109248</v>
+        <v>124.36468152540185</v>
       </c>
       <c r="F661" t="str">
         <v>A</v>
@@ -14197,7 +14197,7 @@
         <v>2012</v>
       </c>
       <c r="E662">
-        <v>233.8398529709624</v>
+        <v>220.51543000673567</v>
       </c>
       <c r="F662" t="str">
         <v>A</v>
@@ -14217,7 +14217,7 @@
         <v>2013</v>
       </c>
       <c r="E663">
-        <v>262.98217678790763</v>
+        <v>265.2297606261196</v>
       </c>
       <c r="F663" t="str">
         <v>A</v>
@@ -14237,7 +14237,7 @@
         <v>2014</v>
       </c>
       <c r="E664">
-        <v>336.8469730858316</v>
+        <v>346.2642577270853</v>
       </c>
       <c r="F664" t="str">
         <v>A</v>
@@ -14257,7 +14257,7 @@
         <v>2015</v>
       </c>
       <c r="E665">
-        <v>354.8377500335672</v>
+        <v>384.1128170617469</v>
       </c>
       <c r="F665" t="str">
         <v>A</v>
@@ -14437,7 +14437,7 @@
         <v>2010</v>
       </c>
       <c r="E674">
-        <v>120.18917429052755</v>
+        <v>117.3354245688704</v>
       </c>
       <c r="F674" t="str">
         <v>A</v>
@@ -14457,7 +14457,7 @@
         <v>2011</v>
       </c>
       <c r="E675">
-        <v>210.15209846229482</v>
+        <v>206.14571796134243</v>
       </c>
       <c r="F675" t="str">
         <v>A</v>
@@ -14477,7 +14477,7 @@
         <v>2012</v>
       </c>
       <c r="E676">
-        <v>214.56451682063326</v>
+        <v>208.4518727787541</v>
       </c>
       <c r="F676" t="str">
         <v>A</v>
@@ -14497,7 +14497,7 @@
         <v>2013</v>
       </c>
       <c r="E677">
-        <v>212.0493277740976</v>
+        <v>215.547400219828</v>
       </c>
       <c r="F677" t="str">
         <v>A</v>
@@ -14517,7 +14517,7 @@
         <v>2014</v>
       </c>
       <c r="E678">
-        <v>238.8656816460458</v>
+        <v>236.57312551014113</v>
       </c>
       <c r="F678" t="str">
         <v>A</v>
@@ -14537,7 +14537,7 @@
         <v>2015</v>
       </c>
       <c r="E679">
-        <v>252.32063375484873</v>
+        <v>253.81122898145753</v>
       </c>
       <c r="F679" t="str">
         <v>A</v>
@@ -14717,7 +14717,7 @@
         <v>2010</v>
       </c>
       <c r="E688">
-        <v>122.5357200149417</v>
+        <v>126.93069355407577</v>
       </c>
       <c r="F688" t="str">
         <v>A</v>
@@ -14737,7 +14737,7 @@
         <v>2011</v>
       </c>
       <c r="E689">
-        <v>132.92789910740433</v>
+        <v>142.5667622134567</v>
       </c>
       <c r="F689" t="str">
         <v>A</v>
@@ -14757,7 +14757,7 @@
         <v>2012</v>
       </c>
       <c r="E690">
-        <v>171.50042367545205</v>
+        <v>183.12170519222198</v>
       </c>
       <c r="F690" t="str">
         <v>A</v>
@@ -14777,7 +14777,7 @@
         <v>2013</v>
       </c>
       <c r="E691">
-        <v>142.58025675286441</v>
+        <v>143.21804026274717</v>
       </c>
       <c r="F691" t="str">
         <v>A</v>
@@ -14797,7 +14797,7 @@
         <v>2014</v>
       </c>
       <c r="E692">
-        <v>146.41915805354563</v>
+        <v>147.49368996021215</v>
       </c>
       <c r="F692" t="str">
         <v>A</v>
@@ -14817,7 +14817,7 @@
         <v>2015</v>
       </c>
       <c r="E693">
-        <v>209.6551171411896</v>
+        <v>213.22112836948318</v>
       </c>
       <c r="F693" t="str">
         <v>A</v>
@@ -14997,7 +14997,7 @@
         <v>2010</v>
       </c>
       <c r="E702">
-        <v>307.8057757660649</v>
+        <v>270.99870638737207</v>
       </c>
       <c r="F702" t="str">
         <v>A</v>
@@ -15017,7 +15017,7 @@
         <v>2011</v>
       </c>
       <c r="E703">
-        <v>361.78687319894084</v>
+        <v>333.8722891501417</v>
       </c>
       <c r="F703" t="str">
         <v>A</v>
@@ -15037,7 +15037,7 @@
         <v>2012</v>
       </c>
       <c r="E704">
-        <v>658.0085826549935</v>
+        <v>665.5761503053947</v>
       </c>
       <c r="F704" t="str">
         <v>A</v>
@@ -15057,7 +15057,7 @@
         <v>2013</v>
       </c>
       <c r="E705">
-        <v>621.4894940905701</v>
+        <v>575.958706831038</v>
       </c>
       <c r="F705" t="str">
         <v>A</v>
@@ -15077,7 +15077,7 @@
         <v>2014</v>
       </c>
       <c r="E706">
-        <v>575.4857645278828</v>
+        <v>541.8358637960918</v>
       </c>
       <c r="F706" t="str">
         <v>A</v>
@@ -15097,7 +15097,7 @@
         <v>2015</v>
       </c>
       <c r="E707">
-        <v>811.5045757196701</v>
+        <v>733.079545937825</v>
       </c>
       <c r="F707" t="str">
         <v>A</v>
@@ -15277,7 +15277,7 @@
         <v>2010</v>
       </c>
       <c r="E716">
-        <v>395.9331779075655</v>
+        <v>407.63094955872054</v>
       </c>
       <c r="F716" t="str">
         <v>A</v>
@@ -15297,7 +15297,7 @@
         <v>2011</v>
       </c>
       <c r="E717">
-        <v>448.9806751766266</v>
+        <v>471.47333359026055</v>
       </c>
       <c r="F717" t="str">
         <v>A</v>
@@ -15317,7 +15317,7 @@
         <v>2012</v>
       </c>
       <c r="E718">
-        <v>509.1920324511606</v>
+        <v>537.180652514633</v>
       </c>
       <c r="F718" t="str">
         <v>A</v>
@@ -15337,7 +15337,7 @@
         <v>2013</v>
       </c>
       <c r="E719">
-        <v>590.3711723098551</v>
+        <v>613.9953120364171</v>
       </c>
       <c r="F719" t="str">
         <v>A</v>
@@ -15357,7 +15357,7 @@
         <v>2014</v>
       </c>
       <c r="E720">
-        <v>589.0319145167897</v>
+        <v>614.6919939524277</v>
       </c>
       <c r="F720" t="str">
         <v>A</v>
@@ -15377,7 +15377,7 @@
         <v>2015</v>
       </c>
       <c r="E721">
-        <v>633.2222787695276</v>
+        <v>659.356855973261</v>
       </c>
       <c r="F721" t="str">
         <v>A</v>
@@ -15557,7 +15557,7 @@
         <v>2010</v>
       </c>
       <c r="E730">
-        <v>92.44358478594113</v>
+        <v>98.43918654582711</v>
       </c>
       <c r="F730" t="str">
         <v>A</v>
@@ -15577,7 +15577,7 @@
         <v>2011</v>
       </c>
       <c r="E731">
-        <v>143.8138669369415</v>
+        <v>157.1088999443374</v>
       </c>
       <c r="F731" t="str">
         <v>A</v>
@@ -15597,7 +15597,7 @@
         <v>2012</v>
       </c>
       <c r="E732">
-        <v>140.58596521231027</v>
+        <v>150.91800809288856</v>
       </c>
       <c r="F732" t="str">
         <v>A</v>
@@ -15617,7 +15617,7 @@
         <v>2013</v>
       </c>
       <c r="E733">
-        <v>155.56861697953747</v>
+        <v>169.53991811916313</v>
       </c>
       <c r="F733" t="str">
         <v>A</v>
@@ -15637,7 +15637,7 @@
         <v>2014</v>
       </c>
       <c r="E734">
-        <v>123.77905118942104</v>
+        <v>136.1888270626156</v>
       </c>
       <c r="F734" t="str">
         <v>A</v>
@@ -15657,7 +15657,7 @@
         <v>2015</v>
       </c>
       <c r="E735">
-        <v>106.63624163955949</v>
+        <v>118.68174960827342</v>
       </c>
       <c r="F735" t="str">
         <v>A</v>
@@ -15837,7 +15837,7 @@
         <v>2010</v>
       </c>
       <c r="E744">
-        <v>92.82342867943238</v>
+        <v>92.35574029461966</v>
       </c>
       <c r="F744" t="str">
         <v>A</v>
@@ -15857,7 +15857,7 @@
         <v>2011</v>
       </c>
       <c r="E745">
-        <v>95.39540649038801</v>
+        <v>95.41491725328576</v>
       </c>
       <c r="F745" t="str">
         <v>A</v>
@@ -15877,7 +15877,7 @@
         <v>2012</v>
       </c>
       <c r="E746">
-        <v>96.47873804981577</v>
+        <v>96.57311745277237</v>
       </c>
       <c r="F746" t="str">
         <v>A</v>
@@ -15897,7 +15897,7 @@
         <v>2013</v>
       </c>
       <c r="E747">
-        <v>102.4889445131035</v>
+        <v>100.59992602968697</v>
       </c>
       <c r="F747" t="str">
         <v>A</v>
@@ -15917,7 +15917,7 @@
         <v>2014</v>
       </c>
       <c r="E748">
-        <v>109.15334079774948</v>
+        <v>108.04319963261062</v>
       </c>
       <c r="F748" t="str">
         <v>A</v>
@@ -15937,7 +15937,7 @@
         <v>2015</v>
       </c>
       <c r="E749">
-        <v>116.2915958282938</v>
+        <v>115.58673670381826</v>
       </c>
       <c r="F749" t="str">
         <v>A</v>
@@ -16117,7 +16117,7 @@
         <v>2010</v>
       </c>
       <c r="E758">
-        <v>39.60151010769836</v>
+        <v>42.72979982301123</v>
       </c>
       <c r="F758" t="str">
         <v>A</v>
@@ -16137,7 +16137,7 @@
         <v>2011</v>
       </c>
       <c r="E759">
-        <v>17.508246994382773</v>
+        <v>18.73683811219678</v>
       </c>
       <c r="F759" t="str">
         <v>A</v>
@@ -16157,7 +16157,7 @@
         <v>2012</v>
       </c>
       <c r="E760">
-        <v>30.870972165933097</v>
+        <v>32.01225357174061</v>
       </c>
       <c r="F760" t="str">
         <v>A</v>
@@ -16177,7 +16177,7 @@
         <v>2013</v>
       </c>
       <c r="E761">
-        <v>40.357296761625726</v>
+        <v>44.46638579697938</v>
       </c>
       <c r="F761" t="str">
         <v>A</v>
@@ -16197,7 +16197,7 @@
         <v>2014</v>
       </c>
       <c r="E762">
-        <v>61.253738367642505</v>
+        <v>67.64038957027813</v>
       </c>
       <c r="F762" t="str">
         <v>A</v>
@@ -16217,7 +16217,7 @@
         <v>2015</v>
       </c>
       <c r="E763">
-        <v>29.19636103405367</v>
+        <v>28.971693751046132</v>
       </c>
       <c r="F763" t="str">
         <v>A</v>
@@ -16397,7 +16397,7 @@
         <v>2010</v>
       </c>
       <c r="E772">
-        <v>30.819504427104636</v>
+        <v>28.744530786188644</v>
       </c>
       <c r="F772" t="str">
         <v>A</v>
@@ -16417,7 +16417,7 @@
         <v>2011</v>
       </c>
       <c r="E773">
-        <v>35.61228268531073</v>
+        <v>33.970537116014555</v>
       </c>
       <c r="F773" t="str">
         <v>A</v>
@@ -16437,7 +16437,7 @@
         <v>2012</v>
       </c>
       <c r="E774">
-        <v>36.534606623044326</v>
+        <v>38.673289431409046</v>
       </c>
       <c r="F774" t="str">
         <v>A</v>
@@ -16457,7 +16457,7 @@
         <v>2013</v>
       </c>
       <c r="E775">
-        <v>37.384213409045465</v>
+        <v>37.552780295742984</v>
       </c>
       <c r="F775" t="str">
         <v>A</v>
@@ -16477,7 +16477,7 @@
         <v>2014</v>
       </c>
       <c r="E776">
-        <v>38.560677045578245</v>
+        <v>38.343106571571475</v>
       </c>
       <c r="F776" t="str">
         <v>A</v>
@@ -16497,7 +16497,7 @@
         <v>2015</v>
       </c>
       <c r="E777">
-        <v>53.78595878515115</v>
+        <v>54.20226919692681</v>
       </c>
       <c r="F777" t="str">
         <v>A</v>
@@ -16677,7 +16677,7 @@
         <v>2010</v>
       </c>
       <c r="E786">
-        <v>22.682434774103893</v>
+        <v>37.36669239389512</v>
       </c>
       <c r="F786" t="str">
         <v>A</v>
@@ -16697,7 +16697,7 @@
         <v>2011</v>
       </c>
       <c r="E787">
-        <v>26.92208668686447</v>
+        <v>40.10093752990068</v>
       </c>
       <c r="F787" t="str">
         <v>A</v>
@@ -16717,7 +16717,7 @@
         <v>2012</v>
       </c>
       <c r="E788">
-        <v>23.22791927161871</v>
+        <v>35.58037968137848</v>
       </c>
       <c r="F788" t="str">
         <v>A</v>
@@ -16737,7 +16737,7 @@
         <v>2013</v>
       </c>
       <c r="E789">
-        <v>36.204363128676725</v>
+        <v>51.874679895152696</v>
       </c>
       <c r="F789" t="str">
         <v>A</v>
@@ -16757,7 +16757,7 @@
         <v>2014</v>
       </c>
       <c r="E790">
-        <v>42.75797135817172</v>
+        <v>59.15214956956346</v>
       </c>
       <c r="F790" t="str">
         <v>A</v>
@@ -16777,7 +16777,7 @@
         <v>2015</v>
       </c>
       <c r="E791">
-        <v>56.53383727901923</v>
+        <v>88.59569427405788</v>
       </c>
       <c r="F791" t="str">
         <v>A</v>
@@ -16957,7 +16957,7 @@
         <v>2010</v>
       </c>
       <c r="E800">
-        <v>1.928334649712369</v>
+        <v>2.041161264572496</v>
       </c>
       <c r="F800" t="str">
         <v>A</v>
@@ -16977,7 +16977,7 @@
         <v>2011</v>
       </c>
       <c r="E801">
-        <v>3.5903151462227876</v>
+        <v>3.816818870344814</v>
       </c>
       <c r="F801" t="str">
         <v>A</v>
@@ -16997,7 +16997,7 @@
         <v>2012</v>
       </c>
       <c r="E802">
-        <v>6.104668728003001</v>
+        <v>5.756818747963454</v>
       </c>
       <c r="F802" t="str">
         <v>A</v>
@@ -17017,7 +17017,7 @@
         <v>2013</v>
       </c>
       <c r="E803">
-        <v>6.581516070482587</v>
+        <v>6.637765164362737</v>
       </c>
       <c r="F803" t="str">
         <v>A</v>
@@ -17037,7 +17037,7 @@
         <v>2014</v>
       </c>
       <c r="E804">
-        <v>9.680214941353475</v>
+        <v>9.950846256980626</v>
       </c>
       <c r="F804" t="str">
         <v>A</v>
@@ -17057,7 +17057,7 @@
         <v>2015</v>
       </c>
       <c r="E805">
-        <v>21.155909934185555</v>
+        <v>22.901329302070813</v>
       </c>
       <c r="F805" t="str">
         <v>A</v>
@@ -17237,7 +17237,7 @@
         <v>2010</v>
       </c>
       <c r="E814">
-        <v>6.2002351816542</v>
+        <v>6.053017934108394</v>
       </c>
       <c r="F814" t="str">
         <v>A</v>
@@ -17257,7 +17257,7 @@
         <v>2011</v>
       </c>
       <c r="E815">
-        <v>10.82660304865548</v>
+        <v>10.62020258126511</v>
       </c>
       <c r="F815" t="str">
         <v>A</v>
@@ -17277,7 +17277,7 @@
         <v>2012</v>
       </c>
       <c r="E816">
-        <v>11.131542601972704</v>
+        <v>10.8144204674692</v>
       </c>
       <c r="F816" t="str">
         <v>A</v>
@@ -17297,7 +17297,7 @@
         <v>2013</v>
       </c>
       <c r="E817">
-        <v>9.310160524812936</v>
+        <v>9.463745619088124</v>
       </c>
       <c r="F817" t="str">
         <v>A</v>
@@ -17317,7 +17317,7 @@
         <v>2014</v>
       </c>
       <c r="E818">
-        <v>16.5954516861148</v>
+        <v>16.436173868016642</v>
       </c>
       <c r="F818" t="str">
         <v>A</v>
@@ -17337,7 +17337,7 @@
         <v>2015</v>
       </c>
       <c r="E819">
-        <v>22.471303260609936</v>
+        <v>22.604053471631076</v>
       </c>
       <c r="F819" t="str">
         <v>A</v>
@@ -17517,7 +17517,7 @@
         <v>2010</v>
       </c>
       <c r="E828">
-        <v>0.4131361020194024</v>
+        <v>0.4279540035767186</v>
       </c>
       <c r="F828" t="str">
         <v>A</v>
@@ -17537,7 +17537,7 @@
         <v>2011</v>
       </c>
       <c r="E829">
-        <v>0.4390953519166611</v>
+        <v>0.4709350185031982</v>
       </c>
       <c r="F829" t="str">
         <v>A</v>
@@ -17557,7 +17557,7 @@
         <v>2012</v>
       </c>
       <c r="E830">
-        <v>0.6591100064390932</v>
+        <v>0.7037728869800999</v>
       </c>
       <c r="F830" t="str">
         <v>A</v>
@@ -17577,7 +17577,7 @@
         <v>2013</v>
       </c>
       <c r="E831">
-        <v>2.772059091560339</v>
+        <v>2.784458940019598</v>
       </c>
       <c r="F831" t="str">
         <v>A</v>
@@ -17597,7 +17597,7 @@
         <v>2014</v>
       </c>
       <c r="E832">
-        <v>2.2077398058788464</v>
+        <v>2.2239418309046086</v>
       </c>
       <c r="F832" t="str">
         <v>A</v>
@@ -17617,7 +17617,7 @@
         <v>2015</v>
       </c>
       <c r="E833">
-        <v>2.3638937535540596</v>
+        <v>2.4041010796742706</v>
       </c>
       <c r="F833" t="str">
         <v>A</v>
@@ -17797,7 +17797,7 @@
         <v>2010</v>
       </c>
       <c r="E842">
-        <v>63.02176789565806</v>
+        <v>51.33109191117529</v>
       </c>
       <c r="F842" t="str">
         <v>A</v>
@@ -17817,7 +17817,7 @@
         <v>2011</v>
       </c>
       <c r="E843">
-        <v>64.53523324679412</v>
+        <v>57.653133860306866</v>
       </c>
       <c r="F843" t="str">
         <v>A</v>
@@ -17837,7 +17837,7 @@
         <v>2012</v>
       </c>
       <c r="E844">
-        <v>107.94807395591891</v>
+        <v>106.41776682185804</v>
       </c>
       <c r="F844" t="str">
         <v>A</v>
@@ -17857,7 +17857,7 @@
         <v>2013</v>
       </c>
       <c r="E845">
-        <v>136.62927283536936</v>
+        <v>123.59159010349589</v>
       </c>
       <c r="F845" t="str">
         <v>A</v>
@@ -17877,7 +17877,7 @@
         <v>2014</v>
       </c>
       <c r="E846">
-        <v>119.50981653573484</v>
+        <v>106.17445989080926</v>
       </c>
       <c r="F846" t="str">
         <v>A</v>
@@ -17897,7 +17897,7 @@
         <v>2015</v>
       </c>
       <c r="E847">
-        <v>155.03900972592822</v>
+        <v>130.9283672642283</v>
       </c>
       <c r="F847" t="str">
         <v>A</v>
@@ -18077,7 +18077,7 @@
         <v>2010</v>
       </c>
       <c r="E856">
-        <v>1888.0632307067583</v>
+        <v>1960.1766063715434</v>
       </c>
       <c r="F856" t="str">
         <v>A</v>
@@ -18097,7 +18097,7 @@
         <v>2011</v>
       </c>
       <c r="E857">
-        <v>2154.952381671985</v>
+        <v>2242.359328676618</v>
       </c>
       <c r="F857" t="str">
         <v>A</v>
@@ -18117,7 +18117,7 @@
         <v>2012</v>
       </c>
       <c r="E858">
-        <v>2362.4959368032864</v>
+        <v>2475.255809279155</v>
       </c>
       <c r="F858" t="str">
         <v>A</v>
@@ -18137,7 +18137,7 @@
         <v>2013</v>
       </c>
       <c r="E859">
-        <v>2343.835767838492</v>
+        <v>2400.764700801627</v>
       </c>
       <c r="F859" t="str">
         <v>A</v>
@@ -18157,7 +18157,7 @@
         <v>2014</v>
       </c>
       <c r="E860">
-        <v>2481.4329946608186</v>
+        <v>2558.6940528937475</v>
       </c>
       <c r="F860" t="str">
         <v>A</v>
@@ -18177,7 +18177,7 @@
         <v>2015</v>
       </c>
       <c r="E861">
-        <v>3181.0403232542467</v>
+        <v>3287.340819756218</v>
       </c>
       <c r="F861" t="str">
         <v>A</v>
@@ -18357,7 +18357,7 @@
         <v>2010</v>
       </c>
       <c r="E870">
-        <v>294.2960772833017</v>
+        <v>313.3832003429826</v>
       </c>
       <c r="F870" t="str">
         <v>A</v>
@@ -18377,7 +18377,7 @@
         <v>2011</v>
       </c>
       <c r="E871">
-        <v>348.44677813241134</v>
+        <v>380.6593283910205</v>
       </c>
       <c r="F871" t="str">
         <v>A</v>
@@ -18397,7 +18397,7 @@
         <v>2012</v>
       </c>
       <c r="E872">
-        <v>351.73484515149704</v>
+        <v>377.5847903946842</v>
       </c>
       <c r="F872" t="str">
         <v>A</v>
@@ -18417,7 +18417,7 @@
         <v>2013</v>
       </c>
       <c r="E873">
-        <v>373.21557834113764</v>
+        <v>406.73331049202153</v>
       </c>
       <c r="F873" t="str">
         <v>A</v>
@@ -18437,7 +18437,7 @@
         <v>2014</v>
       </c>
       <c r="E874">
-        <v>355.1243505930194</v>
+        <v>390.72822342630695</v>
       </c>
       <c r="F874" t="str">
         <v>A</v>
@@ -18457,7 +18457,7 @@
         <v>2015</v>
       </c>
       <c r="E875">
-        <v>378.33689968821704</v>
+        <v>421.0734034320091</v>
       </c>
       <c r="F875" t="str">
         <v>A</v>
@@ -18637,7 +18637,7 @@
         <v>2010</v>
       </c>
       <c r="E884">
-        <v>292.08218915231356</v>
+        <v>290.6105407848634</v>
       </c>
       <c r="F884" t="str">
         <v>A</v>
@@ -18657,7 +18657,7 @@
         <v>2011</v>
       </c>
       <c r="E885">
-        <v>299.9742113716337</v>
+        <v>300.03556365188325</v>
       </c>
       <c r="F885" t="str">
         <v>A</v>
@@ -18677,7 +18677,7 @@
         <v>2012</v>
       </c>
       <c r="E886">
-        <v>304.2686140178179</v>
+        <v>304.56626188002986</v>
       </c>
       <c r="F886" t="str">
         <v>A</v>
@@ -18697,7 +18697,7 @@
         <v>2013</v>
       </c>
       <c r="E887">
-        <v>323.5764178690955</v>
+        <v>317.6124396365528</v>
       </c>
       <c r="F887" t="str">
         <v>A</v>
@@ -18717,7 +18717,7 @@
         <v>2014</v>
       </c>
       <c r="E888">
-        <v>344.9284930601192</v>
+        <v>341.4204069458804</v>
       </c>
       <c r="F888" t="str">
         <v>A</v>
@@ -18737,7 +18737,7 @@
         <v>2015</v>
       </c>
       <c r="E889">
-        <v>367.6260854529042</v>
+        <v>365.3978539209429</v>
       </c>
       <c r="F889" t="str">
         <v>A</v>
@@ -18917,7 +18917,7 @@
         <v>2010</v>
       </c>
       <c r="E898">
-        <v>190.23107244672045</v>
+        <v>205.2582243368785</v>
       </c>
       <c r="F898" t="str">
         <v>A</v>
@@ -18937,7 +18937,7 @@
         <v>2011</v>
       </c>
       <c r="E899">
-        <v>210.95331901292403</v>
+        <v>225.7563643489771</v>
       </c>
       <c r="F899" t="str">
         <v>A</v>
@@ -18957,7 +18957,7 @@
         <v>2012</v>
       </c>
       <c r="E900">
-        <v>221.4667215297463</v>
+        <v>229.65421397178773</v>
       </c>
       <c r="F900" t="str">
         <v>A</v>
@@ -18977,7 +18977,7 @@
         <v>2013</v>
       </c>
       <c r="E901">
-        <v>255.59843184911347</v>
+        <v>281.6228883425289</v>
       </c>
       <c r="F901" t="str">
         <v>A</v>
@@ -18997,7 +18997,7 @@
         <v>2014</v>
       </c>
       <c r="E902">
-        <v>248.37194161243963</v>
+        <v>274.2685644451447</v>
       </c>
       <c r="F902" t="str">
         <v>A</v>
@@ -19017,7 +19017,7 @@
         <v>2015</v>
       </c>
       <c r="E903">
-        <v>283.1698916719307</v>
+        <v>280.9908868939973</v>
       </c>
       <c r="F903" t="str">
         <v>A</v>
@@ -19197,7 +19197,7 @@
         <v>2010</v>
       </c>
       <c r="E912">
-        <v>135.54976847584615</v>
+        <v>126.42365818147404</v>
       </c>
       <c r="F912" t="str">
         <v>A</v>
@@ -19217,7 +19217,7 @@
         <v>2011</v>
       </c>
       <c r="E913">
-        <v>181.77435984452353</v>
+        <v>173.39446315204077</v>
       </c>
       <c r="F913" t="str">
         <v>A</v>
@@ -19237,7 +19237,7 @@
         <v>2012</v>
       </c>
       <c r="E914">
-        <v>173.6891114238969</v>
+        <v>183.85661973827757</v>
       </c>
       <c r="F914" t="str">
         <v>A</v>
@@ -19257,7 +19257,7 @@
         <v>2013</v>
       </c>
       <c r="E915">
-        <v>197.93255208694782</v>
+        <v>198.82503773901502</v>
       </c>
       <c r="F915" t="str">
         <v>A</v>
@@ -19277,7 +19277,7 @@
         <v>2014</v>
       </c>
       <c r="E916">
-        <v>252.27079882155576</v>
+        <v>250.84741413324244</v>
       </c>
       <c r="F916" t="str">
         <v>A</v>
@@ -19297,7 +19297,7 @@
         <v>2015</v>
       </c>
       <c r="E917">
-        <v>220.37602193849122</v>
+        <v>222.08176140118573</v>
       </c>
       <c r="F917" t="str">
         <v>A</v>
@@ -19477,7 +19477,7 @@
         <v>2010</v>
       </c>
       <c r="E926">
-        <v>213.31798885282254</v>
+        <v>344.01479861323145</v>
       </c>
       <c r="F926" t="str">
         <v>A</v>
@@ -19497,7 +19497,7 @@
         <v>2011</v>
       </c>
       <c r="E927">
-        <v>261.05597172590717</v>
+        <v>372.74268084340224</v>
       </c>
       <c r="F927" t="str">
         <v>A</v>
@@ -19517,7 +19517,7 @@
         <v>2012</v>
       </c>
       <c r="E928">
-        <v>294.83626269169577</v>
+        <v>416.62009279166256</v>
       </c>
       <c r="F928" t="str">
         <v>A</v>
@@ -19537,7 +19537,7 @@
         <v>2013</v>
       </c>
       <c r="E929">
-        <v>216.7108313265835</v>
+        <v>286.4579856452316</v>
       </c>
       <c r="F929" t="str">
         <v>A</v>
@@ -19557,7 +19557,7 @@
         <v>2014</v>
       </c>
       <c r="E930">
-        <v>184.98059753248936</v>
+        <v>244.81032757589725</v>
       </c>
       <c r="F930" t="str">
         <v>A</v>
@@ -19577,7 +19577,7 @@
         <v>2015</v>
       </c>
       <c r="E931">
-        <v>404.3949789566105</v>
+        <v>618.0710575564825</v>
       </c>
       <c r="F931" t="str">
         <v>A</v>
@@ -19757,7 +19757,7 @@
         <v>2010</v>
       </c>
       <c r="E940">
-        <v>21.98301500672101</v>
+        <v>23.26923841612646</v>
       </c>
       <c r="F940" t="str">
         <v>A</v>
@@ -19777,7 +19777,7 @@
         <v>2011</v>
       </c>
       <c r="E941">
-        <v>79.88451200345702</v>
+        <v>84.9242198651721</v>
       </c>
       <c r="F941" t="str">
         <v>A</v>
@@ -19797,7 +19797,7 @@
         <v>2012</v>
       </c>
       <c r="E942">
-        <v>45.73328097927672</v>
+        <v>43.12735401016689</v>
       </c>
       <c r="F942" t="str">
         <v>A</v>
@@ -19817,7 +19817,7 @@
         <v>2013</v>
       </c>
       <c r="E943">
-        <v>45.74223081339264</v>
+        <v>46.133167948204104</v>
       </c>
       <c r="F943" t="str">
         <v>A</v>
@@ -19837,7 +19837,7 @@
         <v>2014</v>
       </c>
       <c r="E944">
-        <v>78.78959756063651</v>
+        <v>80.99233092707016</v>
       </c>
       <c r="F944" t="str">
         <v>A</v>
@@ -19857,7 +19857,7 @@
         <v>2015</v>
       </c>
       <c r="E945">
-        <v>106.18060957489338</v>
+        <v>114.94079493314213</v>
       </c>
       <c r="F945" t="str">
         <v>A</v>
@@ -20037,7 +20037,7 @@
         <v>2010</v>
       </c>
       <c r="E954">
-        <v>73.92588101203084</v>
+        <v>72.17059844513854</v>
       </c>
       <c r="F954" t="str">
         <v>A</v>
@@ -20057,7 +20057,7 @@
         <v>2011</v>
       </c>
       <c r="E955">
-        <v>99.95274600276579</v>
+        <v>98.04722740203682</v>
       </c>
       <c r="F955" t="str">
         <v>A</v>
@@ -20077,7 +20077,7 @@
         <v>2012</v>
       </c>
       <c r="E956">
-        <v>116.96186067290158</v>
+        <v>113.62978027413288</v>
       </c>
       <c r="F956" t="str">
         <v>A</v>
@@ -20097,7 +20097,7 @@
         <v>2013</v>
       </c>
       <c r="E957">
-        <v>109.08173152206201</v>
+        <v>110.88119867140561</v>
       </c>
       <c r="F957" t="str">
         <v>A</v>
@@ -20117,7 +20117,7 @@
         <v>2014</v>
       </c>
       <c r="E958">
-        <v>151.53551785517942</v>
+        <v>150.08112859811916</v>
       </c>
       <c r="F958" t="str">
         <v>A</v>
@@ -20137,7 +20137,7 @@
         <v>2015</v>
       </c>
       <c r="E959">
-        <v>153.06167706655455</v>
+        <v>153.96589564676714</v>
       </c>
       <c r="F959" t="str">
         <v>A</v>
@@ -20317,7 +20317,7 @@
         <v>2010</v>
       </c>
       <c r="E968">
-        <v>16.937495560576444</v>
+        <v>17.544990622415206</v>
       </c>
       <c r="F968" t="str">
         <v>A</v>
@@ -20337,7 +20337,7 @@
         <v>2011</v>
       </c>
       <c r="E969">
-        <v>9.540292273521514</v>
+        <v>10.232077608531604</v>
       </c>
       <c r="F969" t="str">
         <v>A</v>
@@ -20357,7 +20357,7 @@
         <v>2012</v>
       </c>
       <c r="E970">
-        <v>8.963896087571667</v>
+        <v>9.571311262929358</v>
       </c>
       <c r="F970" t="str">
         <v>A</v>
@@ -20377,7 +20377,7 @@
         <v>2013</v>
       </c>
       <c r="E971">
-        <v>7.351982808051335</v>
+        <v>7.384869362660674</v>
       </c>
       <c r="F971" t="str">
         <v>A</v>
@@ -20397,7 +20397,7 @@
         <v>2014</v>
       </c>
       <c r="E972">
-        <v>11.70399642801366</v>
+        <v>11.789888996749866</v>
       </c>
       <c r="F972" t="str">
         <v>A</v>
@@ -20417,7 +20417,7 @@
         <v>2015</v>
       </c>
       <c r="E973">
-        <v>20.56255310032018</v>
+        <v>20.912300324418432</v>
       </c>
       <c r="F973" t="str">
         <v>A</v>
@@ -20597,7 +20597,7 @@
         <v>2010</v>
       </c>
       <c r="E982">
-        <v>430.3858696039422</v>
+        <v>336.0018091438516</v>
       </c>
       <c r="F982" t="str">
         <v>A</v>
@@ -20617,7 +20617,7 @@
         <v>2011</v>
       </c>
       <c r="E983">
-        <v>421.76736813762795</v>
+        <v>341.7367304164144</v>
       </c>
       <c r="F983" t="str">
         <v>A</v>
@@ -20637,7 +20637,7 @@
         <v>2012</v>
       </c>
       <c r="E984">
-        <v>586.6402724229208</v>
+        <v>521.4138184913885</v>
       </c>
       <c r="F984" t="str">
         <v>A</v>
@@ -20657,7 +20657,7 @@
         <v>2013</v>
       </c>
       <c r="E985">
-        <v>564.212690245942</v>
+        <v>481.2463907625003</v>
       </c>
       <c r="F985" t="str">
         <v>A</v>
@@ -20677,7 +20677,7 @@
         <v>2014</v>
       </c>
       <c r="E986">
-        <v>577.6509565313127</v>
+        <v>520.1331650891565</v>
       </c>
       <c r="F986" t="str">
         <v>A</v>
@@ -20697,7 +20697,7 @@
         <v>2015</v>
       </c>
       <c r="E987">
-        <v>896.9463764429547</v>
+        <v>718.569291017109</v>
       </c>
       <c r="F987" t="str">
         <v>A</v>
@@ -20877,7 +20877,7 @@
         <v>2010</v>
       </c>
       <c r="E996">
-        <v>924.8389438772347</v>
+        <v>941.6685080319821</v>
       </c>
       <c r="F996" t="str">
         <v>A</v>
@@ -20897,7 +20897,7 @@
         <v>2011</v>
       </c>
       <c r="E997">
-        <v>1089.5861208640558</v>
+        <v>1131.6635125081846</v>
       </c>
       <c r="F997" t="str">
         <v>A</v>
@@ -20917,7 +20917,7 @@
         <v>2012</v>
       </c>
       <c r="E998">
-        <v>1153.5906582968037</v>
+        <v>1205.3560995887865</v>
       </c>
       <c r="F998" t="str">
         <v>A</v>
@@ -20937,7 +20937,7 @@
         <v>2013</v>
       </c>
       <c r="E999">
-        <v>1483.2654996476858</v>
+        <v>1538.4897645379674</v>
       </c>
       <c r="F999" t="str">
         <v>A</v>
@@ -20957,7 +20957,7 @@
         <v>2014</v>
       </c>
       <c r="E1000">
-        <v>1656.165287477119</v>
+        <v>1746.517042683286</v>
       </c>
       <c r="F1000" t="str">
         <v>A</v>
@@ -20977,7 +20977,7 @@
         <v>2015</v>
       </c>
       <c r="E1001">
-        <v>1647.4543538893743</v>
+        <v>1731.444909469326</v>
       </c>
       <c r="F1001" t="str">
         <v>A</v>
@@ -21157,7 +21157,7 @@
         <v>2010</v>
       </c>
       <c r="E1010">
-        <v>219.02343567577697</v>
+        <v>233.22861064205188</v>
       </c>
       <c r="F1010" t="str">
         <v>A</v>
@@ -21177,7 +21177,7 @@
         <v>2011</v>
       </c>
       <c r="E1011">
-        <v>331.87934213521066</v>
+        <v>362.56029733193833</v>
       </c>
       <c r="F1011" t="str">
         <v>A</v>
@@ -21197,7 +21197,7 @@
         <v>2012</v>
       </c>
       <c r="E1012">
-        <v>325.6353103045549</v>
+        <v>349.56713013035403</v>
       </c>
       <c r="F1012" t="str">
         <v>A</v>
@@ -21217,7 +21217,7 @@
         <v>2013</v>
       </c>
       <c r="E1013">
-        <v>435.90394112229797</v>
+        <v>475.05158765675515</v>
       </c>
       <c r="F1013" t="str">
         <v>A</v>
@@ -21237,7 +21237,7 @@
         <v>2014</v>
       </c>
       <c r="E1014">
-        <v>513.488071322189</v>
+        <v>564.969091878048</v>
       </c>
       <c r="F1014" t="str">
         <v>A</v>
@@ -21257,7 +21257,7 @@
         <v>2015</v>
       </c>
       <c r="E1015">
-        <v>567.4319446509677</v>
+        <v>631.5284085351605</v>
       </c>
       <c r="F1015" t="str">
         <v>A</v>
@@ -21437,7 +21437,7 @@
         <v>2010</v>
       </c>
       <c r="E1024">
-        <v>118.12563244531033</v>
+        <v>117.5304595775409</v>
       </c>
       <c r="F1024" t="str">
         <v>A</v>
@@ -21457,7 +21457,7 @@
         <v>2011</v>
       </c>
       <c r="E1025">
-        <v>121.081147036121</v>
+        <v>121.10591117978497</v>
       </c>
       <c r="F1025" t="str">
         <v>A</v>
@@ -21477,7 +21477,7 @@
         <v>2012</v>
       </c>
       <c r="E1026">
-        <v>122.82742979792194</v>
+        <v>122.94758455663192</v>
       </c>
       <c r="F1026" t="str">
         <v>A</v>
@@ -21497,7 +21497,7 @@
         <v>2013</v>
       </c>
       <c r="E1027">
-        <v>130.8947493242575</v>
+        <v>128.48217105027516</v>
       </c>
       <c r="F1027" t="str">
         <v>A</v>
@@ -21517,7 +21517,7 @@
         <v>2014</v>
       </c>
       <c r="E1028">
-        <v>139.51647056155335</v>
+        <v>138.09752198835074</v>
       </c>
       <c r="F1028" t="str">
         <v>A</v>
@@ -21537,7 +21537,7 @@
         <v>2015</v>
       </c>
       <c r="E1029">
-        <v>148.49012504094955</v>
+        <v>147.5901062667282</v>
       </c>
       <c r="F1029" t="str">
         <v>A</v>
@@ -21717,7 +21717,7 @@
         <v>2010</v>
       </c>
       <c r="E1038">
-        <v>106.01556066689761</v>
+        <v>114.39017535192986</v>
       </c>
       <c r="F1038" t="str">
         <v>A</v>
@@ -21737,7 +21737,7 @@
         <v>2011</v>
       </c>
       <c r="E1039">
-        <v>76.39049396643293</v>
+        <v>81.750978222949</v>
       </c>
       <c r="F1039" t="str">
         <v>A</v>
@@ -21757,7 +21757,7 @@
         <v>2012</v>
       </c>
       <c r="E1040">
-        <v>71.39049224062505</v>
+        <v>74.0297561066196</v>
       </c>
       <c r="F1040" t="str">
         <v>A</v>
@@ -21777,7 +21777,7 @@
         <v>2013</v>
       </c>
       <c r="E1041">
-        <v>80.64381334376753</v>
+        <v>88.85478473606041</v>
       </c>
       <c r="F1041" t="str">
         <v>A</v>
@@ -21797,7 +21797,7 @@
         <v>2014</v>
       </c>
       <c r="E1042">
-        <v>140.3419274085526</v>
+        <v>154.9747475979815</v>
       </c>
       <c r="F1042" t="str">
         <v>A</v>
@@ -21817,7 +21817,7 @@
         <v>2015</v>
       </c>
       <c r="E1043">
-        <v>92.50841293397038</v>
+        <v>91.79655662540598</v>
       </c>
       <c r="F1043" t="str">
         <v>A</v>
@@ -21997,7 +21997,7 @@
         <v>2010</v>
       </c>
       <c r="E1052">
-        <v>79.56150366272477</v>
+        <v>74.20489504748026</v>
       </c>
       <c r="F1052" t="str">
         <v>A</v>
@@ -22017,7 +22017,7 @@
         <v>2011</v>
       </c>
       <c r="E1053">
-        <v>73.40471357390913</v>
+        <v>70.02071641932267</v>
       </c>
       <c r="F1053" t="str">
         <v>A</v>
@@ -22037,7 +22037,7 @@
         <v>2012</v>
       </c>
       <c r="E1054">
-        <v>80.50874286919772</v>
+        <v>85.22160774479222</v>
       </c>
       <c r="F1054" t="str">
         <v>A</v>
@@ -22057,7 +22057,7 @@
         <v>2013</v>
       </c>
       <c r="E1055">
-        <v>99.77923238904927</v>
+        <v>100.22914086717765</v>
       </c>
       <c r="F1055" t="str">
         <v>A</v>
@@ -22077,7 +22077,7 @@
         <v>2014</v>
       </c>
       <c r="E1056">
-        <v>72.95633411550858</v>
+        <v>72.54469341281694</v>
       </c>
       <c r="F1056" t="str">
         <v>A</v>
@@ -22097,7 +22097,7 @@
         <v>2015</v>
       </c>
       <c r="E1057">
-        <v>114.78796633782477</v>
+        <v>115.67644033015196</v>
       </c>
       <c r="F1057" t="str">
         <v>A</v>
@@ -22277,7 +22277,7 @@
         <v>2010</v>
       </c>
       <c r="E1066">
-        <v>61.86118574755608</v>
+        <v>85.3538491197496</v>
       </c>
       <c r="F1066" t="str">
         <v>A</v>
@@ -22297,7 +22297,7 @@
         <v>2011</v>
       </c>
       <c r="E1067">
-        <v>85.17971689450563</v>
+        <v>107.73158127469546</v>
       </c>
       <c r="F1067" t="str">
         <v>A</v>
@@ -22317,7 +22317,7 @@
         <v>2012</v>
       </c>
       <c r="E1068">
-        <v>110.65507075508941</v>
+        <v>150.03081129141447</v>
       </c>
       <c r="F1068" t="str">
         <v>A</v>
@@ -22337,7 +22337,7 @@
         <v>2013</v>
       </c>
       <c r="E1069">
-        <v>157.93112222374302</v>
+        <v>205.94250068312172</v>
       </c>
       <c r="F1069" t="str">
         <v>A</v>
@@ -22357,7 +22357,7 @@
         <v>2014</v>
       </c>
       <c r="E1070">
-        <v>209.59099199283492</v>
+        <v>283.71288422873505</v>
       </c>
       <c r="F1070" t="str">
         <v>A</v>
@@ -22377,7 +22377,7 @@
         <v>2015</v>
       </c>
       <c r="E1071">
-        <v>145.40238204876414</v>
+        <v>212.2764323590263</v>
       </c>
       <c r="F1071" t="str">
         <v>A</v>
@@ -22557,7 +22557,7 @@
         <v>2010</v>
       </c>
       <c r="E1080">
-        <v>12.984119974729952</v>
+        <v>13.743819181454807</v>
       </c>
       <c r="F1080" t="str">
         <v>A</v>
@@ -22577,7 +22577,7 @@
         <v>2011</v>
       </c>
       <c r="E1081">
-        <v>12.266910082927858</v>
+        <v>13.04079780701145</v>
       </c>
       <c r="F1081" t="str">
         <v>A</v>
@@ -22597,7 +22597,7 @@
         <v>2012</v>
       </c>
       <c r="E1082">
-        <v>31.35109533194762</v>
+        <v>29.564679332761468</v>
       </c>
       <c r="F1082" t="str">
         <v>A</v>
@@ -22617,7 +22617,7 @@
         <v>2013</v>
       </c>
       <c r="E1083">
-        <v>60.01535023127476</v>
+        <v>60.52827294288968</v>
       </c>
       <c r="F1083" t="str">
         <v>A</v>
@@ -22637,7 +22637,7 @@
         <v>2014</v>
       </c>
       <c r="E1084">
-        <v>42.764493854840026</v>
+        <v>43.96006764159795</v>
       </c>
       <c r="F1084" t="str">
         <v>A</v>
@@ -22657,7 +22657,7 @@
         <v>2015</v>
       </c>
       <c r="E1085">
-        <v>21.85776476612536</v>
+        <v>23.66108904194994</v>
       </c>
       <c r="F1085" t="str">
         <v>A</v>
@@ -22837,7 +22837,7 @@
         <v>2010</v>
       </c>
       <c r="E1094">
-        <v>35.77058758646654</v>
+        <v>34.92125731216381</v>
       </c>
       <c r="F1094" t="str">
         <v>A</v>
@@ -22857,7 +22857,7 @@
         <v>2011</v>
       </c>
       <c r="E1095">
-        <v>49.49304250813935</v>
+        <v>48.54949751435479</v>
       </c>
       <c r="F1095" t="str">
         <v>A</v>
@@ -22877,7 +22877,7 @@
         <v>2012</v>
       </c>
       <c r="E1096">
-        <v>44.68749711226722</v>
+        <v>43.414412601289385</v>
       </c>
       <c r="F1096" t="str">
         <v>A</v>
@@ -22897,7 +22897,7 @@
         <v>2013</v>
       </c>
       <c r="E1097">
-        <v>56.833666487290905</v>
+        <v>57.77122325682153</v>
       </c>
       <c r="F1097" t="str">
         <v>A</v>
@@ -22917,7 +22917,7 @@
         <v>2014</v>
       </c>
       <c r="E1098">
-        <v>54.00323212612768</v>
+        <v>53.48492643936563</v>
       </c>
       <c r="F1098" t="str">
         <v>A</v>
@@ -22937,7 +22937,7 @@
         <v>2015</v>
       </c>
       <c r="E1099">
-        <v>60.22309273843463</v>
+        <v>60.57886330397129</v>
       </c>
       <c r="F1099" t="str">
         <v>A</v>
@@ -23117,7 +23117,7 @@
         <v>2010</v>
       </c>
       <c r="E1108">
-        <v>3.7344242758334105</v>
+        <v>3.8683664102101165</v>
       </c>
       <c r="F1108" t="str">
         <v>A</v>
@@ -23137,7 +23137,7 @@
         <v>2011</v>
       </c>
       <c r="E1109">
-        <v>0.5465425767594664</v>
+        <v>0.5861734527034027</v>
       </c>
       <c r="F1109" t="str">
         <v>A</v>
@@ -23157,7 +23157,7 @@
         <v>2012</v>
       </c>
       <c r="E1110">
-        <v>1.3182200128781865</v>
+        <v>1.4075457739601998</v>
       </c>
       <c r="F1110" t="str">
         <v>A</v>
@@ -23177,7 +23177,7 @@
         <v>2013</v>
       </c>
       <c r="E1111">
-        <v>1.0847187749583935</v>
+        <v>1.0895708895728862</v>
       </c>
       <c r="F1111" t="str">
         <v>A</v>
@@ -23197,7 +23197,7 @@
         <v>2014</v>
       </c>
       <c r="E1112">
-        <v>1.9324485703384848</v>
+        <v>1.9466303049859508</v>
       </c>
       <c r="F1112" t="str">
         <v>A</v>
@@ -23217,7 +23217,7 @@
         <v>2015</v>
       </c>
       <c r="E1113">
-        <v>2.8445025828470194</v>
+        <v>2.892884555525089</v>
       </c>
       <c r="F1113" t="str">
         <v>A</v>
@@ -23397,7 +23397,7 @@
         <v>2010</v>
       </c>
       <c r="E1122">
-        <v>180.31534841251448</v>
+        <v>153.2147321845638</v>
       </c>
       <c r="F1122" t="str">
         <v>A</v>
@@ -23417,7 +23417,7 @@
         <v>2011</v>
       </c>
       <c r="E1123">
-        <v>217.18509380813225</v>
+        <v>197.71079641476723</v>
       </c>
       <c r="F1123" t="str">
         <v>A</v>
@@ -23437,7 +23437,7 @@
         <v>2012</v>
       </c>
       <c r="E1124">
-        <v>239.13897693067224</v>
+        <v>215.14519346923714</v>
       </c>
       <c r="F1124" t="str">
         <v>A</v>
@@ -23457,7 +23457,7 @@
         <v>2013</v>
       </c>
       <c r="E1125">
-        <v>301.708143954163</v>
+        <v>251.44551004560788</v>
       </c>
       <c r="F1125" t="str">
         <v>A</v>
@@ -23477,7 +23477,7 @@
         <v>2014</v>
       </c>
       <c r="E1126">
-        <v>297.3113668517533</v>
+        <v>232.40514345150825</v>
       </c>
       <c r="F1126" t="str">
         <v>A</v>
@@ -23497,7 +23497,7 @@
         <v>2015</v>
       </c>
       <c r="E1127">
-        <v>312.4443607024464</v>
+        <v>249.86034552750436</v>
       </c>
       <c r="F1127" t="str">
         <v>A</v>
@@ -23677,7 +23677,7 @@
         <v>2010</v>
       </c>
       <c r="E1136">
-        <v>375.3124568207753</v>
+        <v>385.5977424223328</v>
       </c>
       <c r="F1136" t="str">
         <v>A</v>
@@ -23697,7 +23697,7 @@
         <v>2011</v>
       </c>
       <c r="E1137">
-        <v>445.42234910090554</v>
+        <v>462.39883099383337</v>
       </c>
       <c r="F1137" t="str">
         <v>A</v>
@@ -23717,7 +23717,7 @@
         <v>2012</v>
       </c>
       <c r="E1138">
-        <v>572.2248535973838</v>
+        <v>597.8337014566132</v>
       </c>
       <c r="F1138" t="str">
         <v>A</v>
@@ -23737,7 +23737,7 @@
         <v>2013</v>
       </c>
       <c r="E1139">
-        <v>583.1151359515864</v>
+        <v>601.8393462207652</v>
       </c>
       <c r="F1139" t="str">
         <v>A</v>
@@ -23757,7 +23757,7 @@
         <v>2014</v>
       </c>
       <c r="E1140">
-        <v>738.7618548771696</v>
+        <v>765.7015523732064</v>
       </c>
       <c r="F1140" t="str">
         <v>A</v>
@@ -23777,7 +23777,7 @@
         <v>2015</v>
       </c>
       <c r="E1141">
-        <v>837.180165718026</v>
+        <v>862.931932584444</v>
       </c>
       <c r="F1141" t="str">
         <v>A</v>
@@ -23957,7 +23957,7 @@
         <v>2010</v>
       </c>
       <c r="E1150">
-        <v>46.16426069324652</v>
+        <v>49.15833024709573</v>
       </c>
       <c r="F1150" t="str">
         <v>A</v>
@@ -23977,7 +23977,7 @@
         <v>2011</v>
       </c>
       <c r="E1151">
-        <v>51.089827212176885</v>
+        <v>55.81288315660728</v>
       </c>
       <c r="F1151" t="str">
         <v>A</v>
@@ -23997,7 +23997,7 @@
         <v>2012</v>
       </c>
       <c r="E1152">
-        <v>57.2876147512589</v>
+        <v>61.497836527253284</v>
       </c>
       <c r="F1152" t="str">
         <v>A</v>
@@ -24017,7 +24017,7 @@
         <v>2013</v>
       </c>
       <c r="E1153">
-        <v>61.77806468806568</v>
+        <v>67.32622705100403</v>
       </c>
       <c r="F1153" t="str">
         <v>A</v>
@@ -24037,7 +24037,7 @@
         <v>2014</v>
       </c>
       <c r="E1154">
-        <v>79.57392567891664</v>
+        <v>87.55180702100591</v>
       </c>
       <c r="F1154" t="str">
         <v>A</v>
@@ -24057,7 +24057,7 @@
         <v>2015</v>
       </c>
       <c r="E1155">
-        <v>65.04613004684971</v>
+        <v>72.39366654819868</v>
       </c>
       <c r="F1155" t="str">
         <v>A</v>
@@ -24237,7 +24237,7 @@
         <v>2010</v>
       </c>
       <c r="E1164">
-        <v>93.84104909985477</v>
+        <v>93.3682334615291</v>
       </c>
       <c r="F1164" t="str">
         <v>A</v>
@@ -24257,7 +24257,7 @@
         <v>2011</v>
       </c>
       <c r="E1165">
-        <v>97.5923976585891</v>
+        <v>97.61235776150593</v>
       </c>
       <c r="F1165" t="str">
         <v>A</v>
@@ -24277,7 +24277,7 @@
         <v>2012</v>
       </c>
       <c r="E1166">
-        <v>99.58691995046416</v>
+        <v>99.68433990264427</v>
       </c>
       <c r="F1166" t="str">
         <v>A</v>
@@ -24297,7 +24297,7 @@
         <v>2013</v>
       </c>
       <c r="E1167">
-        <v>107.98548545099212</v>
+        <v>105.99515782173694</v>
       </c>
       <c r="F1167" t="str">
         <v>A</v>
@@ -24317,7 +24317,7 @@
         <v>2014</v>
       </c>
       <c r="E1168">
-        <v>116.82245527484673</v>
+        <v>115.63431558379042</v>
       </c>
       <c r="F1168" t="str">
         <v>A</v>
@@ -24337,7 +24337,7 @@
         <v>2015</v>
       </c>
       <c r="E1169">
-        <v>126.50774224669622</v>
+        <v>125.7409616740825</v>
       </c>
       <c r="F1169" t="str">
         <v>A</v>
@@ -24517,7 +24517,7 @@
         <v>2010</v>
       </c>
       <c r="E1178">
-        <v>62.190760149433636</v>
+        <v>67.10346966060814</v>
       </c>
       <c r="F1178" t="str">
         <v>A</v>
@@ -24537,7 +24537,7 @@
         <v>2011</v>
       </c>
       <c r="E1179">
-        <v>79.15157743347798</v>
+        <v>84.70581281906159</v>
       </c>
       <c r="F1179" t="str">
         <v>A</v>
@@ -24557,7 +24557,7 @@
         <v>2012</v>
       </c>
       <c r="E1180">
-        <v>67.0786843010276</v>
+        <v>69.55854320237039</v>
       </c>
       <c r="F1180" t="str">
         <v>A</v>
@@ -24577,7 +24577,7 @@
         <v>2013</v>
       </c>
       <c r="E1181">
-        <v>51.46329495858877</v>
+        <v>56.703171709664545</v>
       </c>
       <c r="F1181" t="str">
         <v>A</v>
@@ -24597,7 +24597,7 @@
         <v>2014</v>
       </c>
       <c r="E1182">
-        <v>70.62520003971656</v>
+        <v>77.98897130968872</v>
       </c>
       <c r="F1182" t="str">
         <v>A</v>
@@ -24617,7 +24617,7 @@
         <v>2015</v>
       </c>
       <c r="E1183">
-        <v>75.12069150846239</v>
+        <v>74.54263448145245</v>
       </c>
       <c r="F1183" t="str">
         <v>A</v>
@@ -24797,7 +24797,7 @@
         <v>2010</v>
       </c>
       <c r="E1192">
-        <v>20.518131641569166</v>
+        <v>19.136714804780002</v>
       </c>
       <c r="F1192" t="str">
         <v>A</v>
@@ -24817,7 +24817,7 @@
         <v>2011</v>
       </c>
       <c r="E1193">
-        <v>26.744215854034344</v>
+        <v>25.511292981028728</v>
       </c>
       <c r="F1193" t="str">
         <v>A</v>
@@ -24837,7 +24837,7 @@
         <v>2012</v>
       </c>
       <c r="E1194">
-        <v>30.759093106430388</v>
+        <v>32.559685741965126</v>
       </c>
       <c r="F1194" t="str">
         <v>A</v>
@@ -24857,7 +24857,7 @@
         <v>2013</v>
       </c>
       <c r="E1195">
-        <v>27.358600601902282</v>
+        <v>27.48196160665055</v>
       </c>
       <c r="F1195" t="str">
         <v>A</v>
@@ -24877,7 +24877,7 @@
         <v>2014</v>
       </c>
       <c r="E1196">
-        <v>50.303851810321994</v>
+        <v>50.02002295353606</v>
       </c>
       <c r="F1196" t="str">
         <v>A</v>
@@ -24897,7 +24897,7 @@
         <v>2015</v>
       </c>
       <c r="E1197">
-        <v>41.50820740635188</v>
+        <v>41.82948640383957</v>
       </c>
       <c r="F1197" t="str">
         <v>A</v>
@@ -25077,7 +25077,7 @@
         <v>2010</v>
       </c>
       <c r="E1206">
-        <v>27.21892172892467</v>
+        <v>42.26907232359717</v>
       </c>
       <c r="F1206" t="str">
         <v>A</v>
@@ -25097,7 +25097,7 @@
         <v>2011</v>
       </c>
       <c r="E1207">
-        <v>41.70716708047037</v>
+        <v>60.509018681676956</v>
       </c>
       <c r="F1207" t="str">
         <v>A</v>
@@ -25117,7 +25117,7 @@
         <v>2012</v>
       </c>
       <c r="E1208">
-        <v>103.26121412406877</v>
+        <v>153.25875413098828</v>
       </c>
       <c r="F1208" t="str">
         <v>A</v>
@@ -25137,7 +25137,7 @@
         <v>2013</v>
       </c>
       <c r="E1209">
-        <v>92.90864991679778</v>
+        <v>130.9884142620842</v>
       </c>
       <c r="F1209" t="str">
         <v>A</v>
@@ -25157,7 +25157,7 @@
         <v>2014</v>
       </c>
       <c r="E1210">
-        <v>136.00680706779283</v>
+        <v>185.87829321451176</v>
       </c>
       <c r="F1210" t="str">
         <v>A</v>
@@ -25177,7 +25177,7 @@
         <v>2015</v>
       </c>
       <c r="E1211">
-        <v>113.52909157565186</v>
+        <v>174.73183424763533</v>
       </c>
       <c r="F1211" t="str">
         <v>A</v>
@@ -25357,7 +25357,7 @@
         <v>2010</v>
       </c>
       <c r="E1220">
-        <v>9.127450675305214</v>
+        <v>9.661496652309816</v>
       </c>
       <c r="F1220" t="str">
         <v>A</v>
@@ -25377,7 +25377,7 @@
         <v>2011</v>
       </c>
       <c r="E1221">
-        <v>4.687355885346417</v>
+        <v>4.983069080727952</v>
       </c>
       <c r="F1221" t="str">
         <v>A</v>
@@ -25397,7 +25397,7 @@
         <v>2012</v>
       </c>
       <c r="E1222">
-        <v>7.346296265901916</v>
+        <v>6.927697137379749</v>
       </c>
       <c r="F1222" t="str">
         <v>A</v>
@@ -25417,7 +25417,7 @@
         <v>2013</v>
       </c>
       <c r="E1223">
-        <v>52.85618046883144</v>
+        <v>53.30791715464941</v>
       </c>
       <c r="F1223" t="str">
         <v>A</v>
@@ -25437,7 +25437,7 @@
         <v>2014</v>
       </c>
       <c r="E1224">
-        <v>56.365808519273386</v>
+        <v>57.94163643305174</v>
       </c>
       <c r="F1224" t="str">
         <v>A</v>
@@ -25457,7 +25457,7 @@
         <v>2015</v>
       </c>
       <c r="E1225">
-        <v>53.8422921073822</v>
+        <v>58.284425759298706</v>
       </c>
       <c r="F1225" t="str">
         <v>A</v>
@@ -25637,7 +25637,7 @@
         <v>2010</v>
       </c>
       <c r="E1234">
-        <v>3.3385881747368766</v>
+        <v>3.2593173491352885</v>
       </c>
       <c r="F1234" t="str">
         <v>A</v>
@@ -25657,7 +25657,7 @@
         <v>2011</v>
       </c>
       <c r="E1235">
-        <v>7.733287891896773</v>
+        <v>7.585858986617936</v>
       </c>
       <c r="F1235" t="str">
         <v>A</v>
@@ -25677,7 +25677,7 @@
         <v>2012</v>
       </c>
       <c r="E1236">
-        <v>9.840928966961375</v>
+        <v>9.560574616168422</v>
       </c>
       <c r="F1236" t="str">
         <v>A</v>
@@ -25697,7 +25697,7 @@
         <v>2013</v>
       </c>
       <c r="E1237">
-        <v>13.200973878466103</v>
+        <v>13.41874378825928</v>
       </c>
       <c r="F1237" t="str">
         <v>A</v>
@@ -25717,7 +25717,7 @@
         <v>2014</v>
       </c>
       <c r="E1238">
-        <v>17.95573461120618</v>
+        <v>17.783401234247513</v>
       </c>
       <c r="F1238" t="str">
         <v>A</v>
@@ -25737,7 +25737,7 @@
         <v>2015</v>
       </c>
       <c r="E1239">
-        <v>38.650641608249096</v>
+        <v>38.87897197120546</v>
       </c>
       <c r="F1239" t="str">
         <v>A</v>
@@ -25917,7 +25917,7 @@
         <v>2010</v>
       </c>
       <c r="E1248">
-        <v>2.6326755220613935</v>
+        <v>2.727101369929876</v>
       </c>
       <c r="F1248" t="str">
         <v>A</v>
@@ -25937,7 +25937,7 @@
         <v>2011</v>
       </c>
       <c r="E1249">
-        <v>1.6878973989191137</v>
+        <v>1.8102901552516102</v>
       </c>
       <c r="F1249" t="str">
         <v>A</v>
@@ -25957,7 +25957,7 @@
         <v>2012</v>
       </c>
       <c r="E1250">
-        <v>1.0545760103025492</v>
+        <v>1.12603661916816</v>
       </c>
       <c r="F1250" t="str">
         <v>A</v>
@@ -25977,7 +25977,7 @@
         <v>2013</v>
       </c>
       <c r="E1251">
-        <v>1.807864624930656</v>
+        <v>1.8159514826214773</v>
       </c>
       <c r="F1251" t="str">
         <v>A</v>
@@ -25997,7 +25997,7 @@
         <v>2014</v>
       </c>
       <c r="E1252">
-        <v>3.547679013077982</v>
+        <v>3.573714501499308</v>
       </c>
       <c r="F1252" t="str">
         <v>A</v>
@@ -26017,7 +26017,7 @@
         <v>2015</v>
       </c>
       <c r="E1253">
-        <v>11.593744098851706</v>
+        <v>11.790941392188579</v>
       </c>
       <c r="F1253" t="str">
         <v>A</v>
@@ -26197,7 +26197,7 @@
         <v>2010</v>
       </c>
       <c r="E1262">
-        <v>66.67707886901542</v>
+        <v>53.37438395419581</v>
       </c>
       <c r="F1262" t="str">
         <v>A</v>
@@ -26217,7 +26217,7 @@
         <v>2011</v>
       </c>
       <c r="E1263">
-        <v>85.09002638111747</v>
+        <v>71.31939679762013</v>
       </c>
       <c r="F1263" t="str">
         <v>A</v>
@@ -26237,7 +26237,7 @@
         <v>2012</v>
       </c>
       <c r="E1264">
-        <v>133.4701294504202</v>
+        <v>97.18520278787803</v>
       </c>
       <c r="F1264" t="str">
         <v>A</v>
@@ -26257,7 +26257,7 @@
         <v>2013</v>
       </c>
       <c r="E1265">
-        <v>111.45652081406058</v>
+        <v>78.65379825354046</v>
       </c>
       <c r="F1265" t="str">
         <v>A</v>
@@ -26277,7 +26277,7 @@
         <v>2014</v>
       </c>
       <c r="E1266">
-        <v>125.36797887510534</v>
+        <v>81.46140821602705</v>
       </c>
       <c r="F1266" t="str">
         <v>A</v>
@@ -26297,7 +26297,7 @@
         <v>2015</v>
       </c>
       <c r="E1267">
-        <v>219.16790426929845</v>
+        <v>167.2623356494688</v>
       </c>
       <c r="F1267" t="str">
         <v>A</v>
@@ -26477,7 +26477,7 @@
         <v>2010</v>
       </c>
       <c r="E1276">
-        <v>111.98487209944402</v>
+        <v>114.92658601196085</v>
       </c>
       <c r="F1276" t="str">
         <v>A</v>
@@ -26497,7 +26497,7 @@
         <v>2011</v>
       </c>
       <c r="E1277">
-        <v>117.94339008976745</v>
+        <v>123.62268758879186</v>
       </c>
       <c r="F1277" t="str">
         <v>A</v>
@@ -26517,7 +26517,7 @@
         <v>2012</v>
       </c>
       <c r="E1278">
-        <v>135.88979991193457</v>
+        <v>142.91531352451977</v>
       </c>
       <c r="F1278" t="str">
         <v>A</v>
@@ -26537,7 +26537,7 @@
         <v>2013</v>
       </c>
       <c r="E1279">
-        <v>141.5363945208057</v>
+        <v>146.57013666334964</v>
       </c>
       <c r="F1279" t="str">
         <v>A</v>
@@ -26557,7 +26557,7 @@
         <v>2014</v>
       </c>
       <c r="E1280">
-        <v>150.6132924650796</v>
+        <v>156.55699722830056</v>
       </c>
       <c r="F1280" t="str">
         <v>A</v>
@@ -26577,7 +26577,7 @@
         <v>2015</v>
       </c>
       <c r="E1281">
-        <v>173.95115530701705</v>
+        <v>179.4215621186856</v>
       </c>
       <c r="F1281" t="str">
         <v>A</v>
@@ -26757,7 +26757,7 @@
         <v>2010</v>
       </c>
       <c r="E1290">
-        <v>28.83330216181855</v>
+        <v>30.703339953894897</v>
       </c>
       <c r="F1290" t="str">
         <v>A</v>
@@ -26777,7 +26777,7 @@
         <v>2011</v>
       </c>
       <c r="E1291">
-        <v>34.13865157139833</v>
+        <v>37.29463721545822</v>
       </c>
       <c r="F1291" t="str">
         <v>A</v>
@@ -26797,7 +26797,7 @@
         <v>2012</v>
       </c>
       <c r="E1292">
-        <v>34.46079596001806</v>
+        <v>36.99341307453632</v>
       </c>
       <c r="F1292" t="str">
         <v>A</v>
@@ -26817,7 +26817,7 @@
         <v>2013</v>
       </c>
       <c r="E1293">
-        <v>36.56534480902661</v>
+        <v>39.84920407010338</v>
       </c>
       <c r="F1293" t="str">
         <v>A</v>
@@ -26837,7 +26837,7 @@
         <v>2014</v>
       </c>
       <c r="E1294">
-        <v>36.9838896611213</v>
+        <v>40.691801276238756</v>
       </c>
       <c r="F1294" t="str">
         <v>A</v>
@@ -26857,7 +26857,7 @@
         <v>2015</v>
       </c>
       <c r="E1295">
-        <v>37.532869750022556</v>
+        <v>41.772539816328425</v>
       </c>
       <c r="F1295" t="str">
         <v>A</v>
@@ -27037,7 +27037,7 @@
         <v>2010</v>
       </c>
       <c r="E1304">
-        <v>16.697102871298295</v>
+        <v>16.612974961092586</v>
       </c>
       <c r="F1304" t="str">
         <v>A</v>
@@ -27057,7 +27057,7 @@
         <v>2011</v>
       </c>
       <c r="E1305">
-        <v>17.117117080926285</v>
+        <v>17.120617962416766</v>
       </c>
       <c r="F1305" t="str">
         <v>A</v>
@@ -27077,7 +27077,7 @@
         <v>2012</v>
       </c>
       <c r="E1306">
-        <v>17.34795797693136</v>
+        <v>17.36492845093915</v>
       </c>
       <c r="F1306" t="str">
         <v>A</v>
@@ -27097,7 +27097,7 @@
         <v>2013</v>
       </c>
       <c r="E1307">
-        <v>18.469085904106308</v>
+        <v>18.12867411812871</v>
       </c>
       <c r="F1307" t="str">
         <v>A</v>
@@ -27117,7 +27117,7 @@
         <v>2014</v>
       </c>
       <c r="E1308">
-        <v>19.669999520929146</v>
+        <v>19.469946311134073</v>
       </c>
       <c r="F1308" t="str">
         <v>A</v>
@@ -27137,7 +27137,7 @@
         <v>2015</v>
       </c>
       <c r="E1309">
-        <v>20.911122176818363</v>
+        <v>20.784377031011648</v>
       </c>
       <c r="F1309" t="str">
         <v>A</v>
@@ -27317,7 +27317,7 @@
         <v>2010</v>
       </c>
       <c r="E1318">
-        <v>12.099722129138176</v>
+        <v>13.055530031205231</v>
       </c>
       <c r="F1318" t="str">
         <v>A</v>
@@ -27337,7 +27337,7 @@
         <v>2011</v>
       </c>
       <c r="E1319">
-        <v>13.279392481012692</v>
+        <v>14.211235837881752</v>
       </c>
       <c r="F1319" t="str">
         <v>A</v>
@@ -27357,7 +27357,7 @@
         <v>2012</v>
       </c>
       <c r="E1320">
-        <v>13.761194754266713</v>
+        <v>14.269937906582198</v>
       </c>
       <c r="F1320" t="str">
         <v>A</v>
@@ -27377,7 +27377,7 @@
         <v>2013</v>
       </c>
       <c r="E1321">
-        <v>15.66096515139788</v>
+        <v>17.25552934053988</v>
       </c>
       <c r="F1321" t="str">
         <v>A</v>
@@ -27397,7 +27397,7 @@
         <v>2014</v>
       </c>
       <c r="E1322">
-        <v>15.077157447176054</v>
+        <v>16.649184694956254</v>
       </c>
       <c r="F1322" t="str">
         <v>A</v>
@@ -27417,7 +27417,7 @@
         <v>2015</v>
       </c>
       <c r="E1323">
-        <v>17.094687286806376</v>
+        <v>16.96314291584485</v>
       </c>
       <c r="F1323" t="str">
         <v>A</v>
@@ -27597,7 +27597,7 @@
         <v>2010</v>
       </c>
       <c r="E1332">
-        <v>8.621696298779538</v>
+        <v>8.04122646668785</v>
       </c>
       <c r="F1332" t="str">
         <v>A</v>
@@ -27617,7 +27617,7 @@
         <v>2011</v>
       </c>
       <c r="E1333">
-        <v>11.442593454584978</v>
+        <v>10.915083682989486</v>
       </c>
       <c r="F1333" t="str">
         <v>A</v>
@@ -27637,7 +27637,7 @@
         <v>2012</v>
       </c>
       <c r="E1334">
-        <v>10.792455283981528</v>
+        <v>11.424229941200291</v>
       </c>
       <c r="F1334" t="str">
         <v>A</v>
@@ -27657,7 +27657,7 @@
         <v>2013</v>
       </c>
       <c r="E1335">
-        <v>12.127675346579741</v>
+        <v>12.18235951108744</v>
       </c>
       <c r="F1335" t="str">
         <v>A</v>
@@ -27677,7 +27677,7 @@
         <v>2014</v>
       </c>
       <c r="E1336">
-        <v>15.313833472753966</v>
+        <v>15.227428402542426</v>
       </c>
       <c r="F1336" t="str">
         <v>A</v>
@@ -27697,7 +27697,7 @@
         <v>2015</v>
       </c>
       <c r="E1337">
-        <v>13.30388325646388</v>
+        <v>13.406857066763283</v>
       </c>
       <c r="F1337" t="str">
         <v>A</v>
@@ -27877,7 +27877,7 @@
         <v>2010</v>
       </c>
       <c r="E1346">
-        <v>1.8558355724266822</v>
+        <v>2.46059187908997</v>
       </c>
       <c r="F1346" t="str">
         <v>A</v>
@@ -27897,7 +27897,7 @@
         <v>2011</v>
       </c>
       <c r="E1347">
-        <v>3.972111150520988</v>
+        <v>5.6607800261482675</v>
       </c>
       <c r="F1347" t="str">
         <v>A</v>
@@ -27917,7 +27917,7 @@
         <v>2012</v>
       </c>
       <c r="E1348">
-        <v>5.412998433431439</v>
+        <v>7.849070368163284</v>
       </c>
       <c r="F1348" t="str">
         <v>A</v>
@@ -27937,7 +27937,7 @@
         <v>2013</v>
       </c>
       <c r="E1349">
-        <v>2.9642922175602133</v>
+        <v>3.9945475217606616</v>
       </c>
       <c r="F1349" t="str">
         <v>A</v>
@@ -27957,7 +27957,7 @@
         <v>2014</v>
       </c>
       <c r="E1350">
-        <v>5.6354217641854865</v>
+        <v>6.928431169728517</v>
       </c>
       <c r="F1350" t="str">
         <v>A</v>
@@ -27977,7 +27977,7 @@
         <v>2015</v>
       </c>
       <c r="E1351">
-        <v>9.06155129635838</v>
+        <v>13.245953896230226</v>
       </c>
       <c r="F1351" t="str">
         <v>A</v>
@@ -28157,7 +28157,7 @@
         <v>2010</v>
       </c>
       <c r="E1360">
-        <v>8.09900552879195</v>
+        <v>8.572877311204484</v>
       </c>
       <c r="F1360" t="str">
         <v>A</v>
@@ -28177,7 +28177,7 @@
         <v>2011</v>
       </c>
       <c r="E1361">
-        <v>1.9946195256793262</v>
+        <v>2.120454927969341</v>
       </c>
       <c r="F1361" t="str">
         <v>A</v>
@@ -28197,7 +28197,7 @@
         <v>2012</v>
       </c>
       <c r="E1362">
-        <v>6.725482496952458</v>
+        <v>6.342257942671601</v>
       </c>
       <c r="F1362" t="str">
         <v>A</v>
@@ -28217,7 +28217,7 @@
         <v>2013</v>
       </c>
       <c r="E1363">
-        <v>8.7041050209388</v>
+        <v>8.778494875073058</v>
       </c>
       <c r="F1363" t="str">
         <v>A</v>
@@ -28237,7 +28237,7 @@
         <v>2014</v>
       </c>
       <c r="E1364">
-        <v>6.0041839509660795</v>
+        <v>6.172043880912034</v>
       </c>
       <c r="F1364" t="str">
         <v>A</v>
@@ -28257,7 +28257,7 @@
         <v>2015</v>
       </c>
       <c r="E1365">
-        <v>8.121463055303458</v>
+        <v>8.791505561458463</v>
       </c>
       <c r="F1365" t="str">
         <v>A</v>
@@ -28437,7 +28437,7 @@
         <v>2010</v>
       </c>
       <c r="E1374">
-        <v>0.7154117517293307</v>
+        <v>0.6984251462432761</v>
       </c>
       <c r="F1374" t="str">
         <v>A</v>
@@ -28457,7 +28457,7 @@
         <v>2011</v>
       </c>
       <c r="E1375">
-        <v>1.353325381081935</v>
+        <v>1.3275253226581387</v>
       </c>
       <c r="F1375" t="str">
         <v>A</v>
@@ -28477,7 +28477,7 @@
         <v>2012</v>
       </c>
       <c r="E1376">
-        <v>0.9679602262584958</v>
+        <v>0.9403843884755824</v>
       </c>
       <c r="F1376" t="str">
         <v>A</v>
@@ -28497,7 +28497,7 @@
         <v>2013</v>
       </c>
       <c r="E1377">
-        <v>0.9727033384132917</v>
+        <v>0.9887495422927889</v>
       </c>
       <c r="F1377" t="str">
         <v>A</v>
@@ -28517,7 +28517,7 @@
         <v>2014</v>
       </c>
       <c r="E1378">
-        <v>1.904396095127928</v>
+        <v>1.8861183127232208</v>
       </c>
       <c r="F1378" t="str">
         <v>A</v>
@@ -28537,7 +28537,7 @@
         <v>2015</v>
       </c>
       <c r="E1379">
-        <v>2.4397414968662217</v>
+        <v>2.4541543769199454</v>
       </c>
       <c r="F1379" t="str">
         <v>A</v>
@@ -28717,7 +28717,7 @@
         <v>2010</v>
       </c>
       <c r="E1388">
-        <v>0.0374544543709155</v>
+        <v>0.038797828660982144</v>
       </c>
       <c r="F1388" t="str">
         <v>A</v>
@@ -28737,7 +28737,7 @@
         <v>2011</v>
       </c>
       <c r="E1389">
-        <v>0.002145318606253987</v>
+        <v>0.0023008798729512157</v>
       </c>
       <c r="F1389" t="str">
         <v>A</v>
@@ -28757,7 +28757,7 @@
         <v>2012</v>
       </c>
       <c r="E1390">
-        <v>0.13182200128781865</v>
+        <v>0.14075457739602</v>
       </c>
       <c r="F1390" t="str">
         <v>A</v>
@@ -28797,7 +28797,7 @@
         <v>2014</v>
       </c>
       <c r="E1392">
-        <v>0.11151815571018678</v>
+        <v>0.11233655828862106</v>
       </c>
       <c r="F1392" t="str">
         <v>A</v>
@@ -28817,7 +28817,7 @@
         <v>2015</v>
       </c>
       <c r="E1393">
-        <v>0.1007222274587856</v>
+        <v>0.10243540574393514</v>
       </c>
       <c r="F1393" t="str">
         <v>A</v>
@@ -28997,7 +28997,7 @@
         <v>2010</v>
       </c>
       <c r="E1402">
-        <v>22.015016757256817</v>
+        <v>21.16983489325085</v>
       </c>
       <c r="F1402" t="str">
         <v>A</v>
@@ -29017,7 +29017,7 @@
         <v>2011</v>
       </c>
       <c r="E1403">
-        <v>21.42019250727614</v>
+        <v>20.921075606738825</v>
       </c>
       <c r="F1403" t="str">
         <v>A</v>
@@ -29037,7 +29037,7 @@
         <v>2012</v>
       </c>
       <c r="E1404">
-        <v>31.43751274387307</v>
+        <v>31.699128593938866</v>
       </c>
       <c r="F1404" t="str">
         <v>A</v>
@@ -29057,7 +29057,7 @@
         <v>2013</v>
       </c>
       <c r="E1405">
-        <v>30.950600698815308</v>
+        <v>29.283092796292294</v>
       </c>
       <c r="F1405" t="str">
         <v>A</v>
@@ -29077,7 +29077,7 @@
         <v>2014</v>
       </c>
       <c r="E1406">
-        <v>33.156112110612526</v>
+        <v>31.454028797232702</v>
       </c>
       <c r="F1406" t="str">
         <v>A</v>
@@ -29097,7 +29097,7 @@
         <v>2015</v>
       </c>
       <c r="E1407">
-        <v>46.22474291515381</v>
+        <v>41.63316064494264</v>
       </c>
       <c r="F1407" t="str">
         <v>A</v>
@@ -29277,7 +29277,7 @@
         <v>2010</v>
       </c>
       <c r="E1416">
-        <v>1446.6873781484996</v>
+        <v>1463.3966933283912</v>
       </c>
       <c r="F1416" t="str">
         <v>A</v>
@@ -29297,7 +29297,7 @@
         <v>2011</v>
       </c>
       <c r="E1417">
-        <v>1581.6603871455336</v>
+        <v>1648.0793679283915</v>
       </c>
       <c r="F1417" t="str">
         <v>A</v>
@@ -29317,7 +29317,7 @@
         <v>2012</v>
       </c>
       <c r="E1418">
-        <v>1538.6167258902185</v>
+        <v>1601.8894651505398</v>
       </c>
       <c r="F1418" t="str">
         <v>A</v>
@@ -29337,7 +29337,7 @@
         <v>2013</v>
       </c>
       <c r="E1419">
-        <v>1862.1445854708827</v>
+        <v>1919.1870313580698</v>
       </c>
       <c r="F1419" t="str">
         <v>A</v>
@@ -29357,7 +29357,7 @@
         <v>2014</v>
       </c>
       <c r="E1420">
-        <v>1903.8141172640858</v>
+        <v>1962.390910073357</v>
       </c>
       <c r="F1420" t="str">
         <v>A</v>
@@ -29377,7 +29377,7 @@
         <v>2015</v>
       </c>
       <c r="E1421">
-        <v>2086.2075419802563</v>
+        <v>2134.150578164476</v>
       </c>
       <c r="F1421" t="str">
         <v>A</v>
@@ -29557,7 +29557,7 @@
         <v>2010</v>
       </c>
       <c r="E1430">
-        <v>297.6184870044531</v>
+        <v>316.92109116666074</v>
       </c>
       <c r="F1430" t="str">
         <v>A</v>
@@ -29577,7 +29577,7 @@
         <v>2011</v>
       </c>
       <c r="E1431">
-        <v>370.3863225984881</v>
+        <v>404.62709846604787</v>
       </c>
       <c r="F1431" t="str">
         <v>A</v>
@@ -29597,7 +29597,7 @@
         <v>2012</v>
       </c>
       <c r="E1432">
-        <v>328.2550981035692</v>
+        <v>352.3794532214692</v>
       </c>
       <c r="F1432" t="str">
         <v>A</v>
@@ -29617,7 +29617,7 @@
         <v>2013</v>
       </c>
       <c r="E1433">
-        <v>353.0432718354409</v>
+        <v>384.74937015976076</v>
       </c>
       <c r="F1433" t="str">
         <v>A</v>
@@ -29637,7 +29637,7 @@
         <v>2014</v>
       </c>
       <c r="E1434">
-        <v>377.590615969487</v>
+        <v>415.4468999769644</v>
       </c>
       <c r="F1434" t="str">
         <v>A</v>
@@ -29657,7 +29657,7 @@
         <v>2015</v>
       </c>
       <c r="E1435">
-        <v>362.3792840087547</v>
+        <v>403.3132337251988</v>
       </c>
       <c r="F1435" t="str">
         <v>A</v>
@@ -29837,7 +29837,7 @@
         <v>2010</v>
       </c>
       <c r="E1444">
-        <v>131.35959141452474</v>
+        <v>130.69773959529832</v>
       </c>
       <c r="F1444" t="str">
         <v>A</v>
@@ -29857,7 +29857,7 @@
         <v>2011</v>
       </c>
       <c r="E1445">
-        <v>134.9252253809465</v>
+        <v>134.95282098725696</v>
       </c>
       <c r="F1445" t="str">
         <v>A</v>
@@ -29877,7 +29877,7 @@
         <v>2012</v>
       </c>
       <c r="E1446">
-        <v>136.74250928816664</v>
+        <v>136.8762763403304</v>
       </c>
       <c r="F1446" t="str">
         <v>A</v>
@@ -29897,7 +29897,7 @@
         <v>2013</v>
       </c>
       <c r="E1447">
-        <v>145.50118558246768</v>
+        <v>142.81938970458</v>
       </c>
       <c r="F1447" t="str">
         <v>A</v>
@@ -29917,7 +29917,7 @@
         <v>2014</v>
       </c>
       <c r="E1448">
-        <v>155.29968674541186</v>
+        <v>153.72021538952637</v>
       </c>
       <c r="F1448" t="str">
         <v>A</v>
@@ -29937,7 +29937,7 @@
         <v>2015</v>
       </c>
       <c r="E1449">
-        <v>165.21426663196112</v>
+        <v>164.2128805687669</v>
       </c>
       <c r="F1449" t="str">
         <v>A</v>
@@ -30117,7 +30117,7 @@
         <v>2010</v>
       </c>
       <c r="E1458">
-        <v>116.9747831487128</v>
+        <v>126.21511287553139</v>
       </c>
       <c r="F1458" t="str">
         <v>A</v>
@@ -30137,7 +30137,7 @@
         <v>2011</v>
       </c>
       <c r="E1459">
-        <v>94.62833435941462</v>
+        <v>101.2686068621278</v>
       </c>
       <c r="F1459" t="str">
         <v>A</v>
@@ -30157,7 +30157,7 @@
         <v>2012</v>
       </c>
       <c r="E1460">
-        <v>136.7524772155619</v>
+        <v>141.80813463397214</v>
       </c>
       <c r="F1460" t="str">
         <v>A</v>
@@ -30177,7 +30177,7 @@
         <v>2013</v>
       </c>
       <c r="E1461">
-        <v>196.38284163437947</v>
+        <v>216.3781001388769</v>
       </c>
       <c r="F1461" t="str">
         <v>A</v>
@@ -30197,7 +30197,7 @@
         <v>2014</v>
       </c>
       <c r="E1462">
-        <v>174.80018053430558</v>
+        <v>193.0258074589813</v>
       </c>
       <c r="F1462" t="str">
         <v>A</v>
@@ -30217,7 +30217,7 @@
         <v>2015</v>
       </c>
       <c r="E1463">
-        <v>179.12372364269592</v>
+        <v>177.74535870652943</v>
       </c>
       <c r="F1463" t="str">
         <v>A</v>
@@ -30397,7 +30397,7 @@
         <v>2010</v>
       </c>
       <c r="E1472">
-        <v>85.60559586361599</v>
+        <v>79.84205883621033</v>
       </c>
       <c r="F1472" t="str">
         <v>A</v>
@@ -30417,7 +30417,7 @@
         <v>2011</v>
       </c>
       <c r="E1473">
-        <v>74.16377248321717</v>
+        <v>70.74478230074189</v>
       </c>
       <c r="F1473" t="str">
         <v>A</v>
@@ -30437,7 +30437,7 @@
         <v>2012</v>
       </c>
       <c r="E1474">
-        <v>68.04135096118985</v>
+        <v>72.02439282229531</v>
       </c>
       <c r="F1474" t="str">
         <v>A</v>
@@ -30457,7 +30457,7 @@
         <v>2013</v>
       </c>
       <c r="E1475">
-        <v>107.4213815627216</v>
+        <v>107.90574879165447</v>
       </c>
       <c r="F1475" t="str">
         <v>A</v>
@@ -30477,7 +30477,7 @@
         <v>2014</v>
       </c>
       <c r="E1476">
-        <v>86.0041439849128</v>
+        <v>85.51888377147759</v>
       </c>
       <c r="F1476" t="str">
         <v>A</v>
@@ -30497,7 +30497,7 @@
         <v>2015</v>
       </c>
       <c r="E1477">
-        <v>116.61104156450679</v>
+        <v>117.51362639943048</v>
       </c>
       <c r="F1477" t="str">
         <v>A</v>
@@ -30677,7 +30677,7 @@
         <v>2010</v>
       </c>
       <c r="E1486">
-        <v>79.0792157806259</v>
+        <v>91.74058940784137</v>
       </c>
       <c r="F1486" t="str">
         <v>A</v>
@@ -30697,7 +30697,7 @@
         <v>2011</v>
       </c>
       <c r="E1487">
-        <v>82.86265205670203</v>
+        <v>103.53808190355433</v>
       </c>
       <c r="F1487" t="str">
         <v>A</v>
@@ -30717,7 +30717,7 @@
         <v>2012</v>
       </c>
       <c r="E1488">
-        <v>75.35630676154477</v>
+        <v>95.05157705016205</v>
       </c>
       <c r="F1488" t="str">
         <v>A</v>
@@ -30737,7 +30737,7 @@
         <v>2013</v>
       </c>
       <c r="E1489">
-        <v>119.29955939291277</v>
+        <v>148.5705785133053</v>
       </c>
       <c r="F1489" t="str">
         <v>A</v>
@@ -30757,7 +30757,7 @@
         <v>2014</v>
       </c>
       <c r="E1490">
-        <v>150.88260777017925</v>
+        <v>184.5277202883376</v>
       </c>
       <c r="F1490" t="str">
         <v>A</v>
@@ -30777,7 +30777,7 @@
         <v>2015</v>
       </c>
       <c r="E1491">
-        <v>130.0589662395944</v>
+        <v>180.34206334629775</v>
       </c>
       <c r="F1491" t="str">
         <v>A</v>
@@ -30957,7 +30957,7 @@
         <v>2010</v>
       </c>
       <c r="E1500">
-        <v>32.52457775848196</v>
+        <v>34.42758666245611</v>
       </c>
       <c r="F1500" t="str">
         <v>A</v>
@@ -30977,7 +30977,7 @@
         <v>2011</v>
       </c>
       <c r="E1501">
-        <v>32.21310533972112</v>
+        <v>34.245347086704854</v>
       </c>
       <c r="F1501" t="str">
         <v>A</v>
@@ -30997,7 +30997,7 @@
         <v>2012</v>
       </c>
       <c r="E1502">
-        <v>37.35229509845904</v>
+        <v>35.2239248816069</v>
       </c>
       <c r="F1502" t="str">
         <v>A</v>
@@ -31017,7 +31017,7 @@
         <v>2013</v>
       </c>
       <c r="E1503">
-        <v>57.36920839407767</v>
+        <v>57.85951578742447</v>
       </c>
       <c r="F1503" t="str">
         <v>A</v>
@@ -31037,7 +31037,7 @@
         <v>2014</v>
       </c>
       <c r="E1504">
-        <v>44.35744061734084</v>
+        <v>45.59754867122727</v>
       </c>
       <c r="F1504" t="str">
         <v>A</v>
@@ -31057,7 +31057,7 @@
         <v>2015</v>
       </c>
       <c r="E1505">
-        <v>38.20095585272368</v>
+        <v>41.35263727056388</v>
       </c>
       <c r="F1505" t="str">
         <v>A</v>
@@ -31237,7 +31237,7 @@
         <v>2010</v>
       </c>
       <c r="E1514">
-        <v>82.98776320060234</v>
+        <v>81.01731696422003</v>
       </c>
       <c r="F1514" t="str">
         <v>A</v>
@@ -31257,7 +31257,7 @@
         <v>2011</v>
       </c>
       <c r="E1515">
-        <v>111.93934223520579</v>
+        <v>109.80530883129462</v>
       </c>
       <c r="F1515" t="str">
         <v>A</v>
@@ -31277,7 +31277,7 @@
         <v>2012</v>
       </c>
       <c r="E1516">
-        <v>69.85446299498811</v>
+        <v>67.86440670165452</v>
       </c>
       <c r="F1516" t="str">
         <v>A</v>
@@ -31297,7 +31297,7 @@
         <v>2013</v>
       </c>
       <c r="E1517">
-        <v>61.97509841890402</v>
+        <v>62.99747083751198</v>
       </c>
       <c r="F1517" t="str">
         <v>A</v>
@@ -31317,7 +31317,7 @@
         <v>2014</v>
       </c>
       <c r="E1518">
-        <v>82.02506038301004</v>
+        <v>81.23781018372159</v>
       </c>
       <c r="F1518" t="str">
         <v>A</v>
@@ -31337,7 +31337,7 @@
         <v>2015</v>
       </c>
       <c r="E1519">
-        <v>112.35651630304957</v>
+        <v>113.02026735815528</v>
       </c>
       <c r="F1519" t="str">
         <v>A</v>
@@ -31517,7 +31517,7 @@
         <v>2010</v>
       </c>
       <c r="E1528">
-        <v>247.48341242427384</v>
+        <v>256.3598694185826</v>
       </c>
       <c r="F1528" t="str">
         <v>A</v>
@@ -31537,7 +31537,7 @@
         <v>2011</v>
       </c>
       <c r="E1529">
-        <v>279.1435995043957</v>
+        <v>299.3848502923855</v>
       </c>
       <c r="F1529" t="str">
         <v>A</v>
@@ -31557,7 +31557,7 @@
         <v>2012</v>
       </c>
       <c r="E1530">
-        <v>227.524774222775</v>
+        <v>242.9424005855305</v>
       </c>
       <c r="F1530" t="str">
         <v>A</v>
@@ -31577,7 +31577,7 @@
         <v>2013</v>
       </c>
       <c r="E1531">
-        <v>249.00322100711566</v>
+        <v>250.11705087306476</v>
       </c>
       <c r="F1531" t="str">
         <v>A</v>
@@ -31597,7 +31597,7 @@
         <v>2014</v>
       </c>
       <c r="E1532">
-        <v>282.17462300373523</v>
+        <v>284.245428762352</v>
       </c>
       <c r="F1532" t="str">
         <v>A</v>
@@ -31617,7 +31617,7 @@
         <v>2015</v>
       </c>
       <c r="E1533">
-        <v>316.4191679949566</v>
+        <v>321.8011225177143</v>
       </c>
       <c r="F1533" t="str">
         <v>A</v>
@@ -31797,7 +31797,7 @@
         <v>2010</v>
       </c>
       <c r="E1542">
-        <v>204.97881788813243</v>
+        <v>173.34617046002165</v>
       </c>
       <c r="F1542" t="str">
         <v>A</v>
@@ -31817,7 +31817,7 @@
         <v>2011</v>
       </c>
       <c r="E1543">
-        <v>224.06993161258652</v>
+        <v>202.21814726414107</v>
       </c>
       <c r="F1543" t="str">
         <v>A</v>
@@ -31837,7 +31837,7 @@
         <v>2012</v>
       </c>
       <c r="E1544">
-        <v>290.5794952596</v>
+        <v>279.5997141638374</v>
       </c>
       <c r="F1544" t="str">
         <v>A</v>
@@ -31857,7 +31857,7 @@
         <v>2013</v>
       </c>
       <c r="E1545">
-        <v>373.1989525609845</v>
+        <v>336.85246840873555</v>
       </c>
       <c r="F1545" t="str">
         <v>A</v>
@@ -31877,7 +31877,7 @@
         <v>2014</v>
       </c>
       <c r="E1546">
-        <v>338.8671463195956</v>
+        <v>293.87668229725585</v>
       </c>
       <c r="F1546" t="str">
         <v>A</v>
@@ -31897,7 +31897,7 @@
         <v>2015</v>
       </c>
       <c r="E1547">
-        <v>436.0520315158151</v>
+        <v>373.7760274482442</v>
       </c>
       <c r="F1547" t="str">
         <v>A</v>
